--- a/projects/finance-release/Cash_Working_Capital.xlsx
+++ b/projects/finance-release/Cash_Working_Capital.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf925ec36ec414197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rbce05f0c13b24126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly" sheetId="3" r:id="R07fc89065ebf405c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="4" r:id="R1027f78f7ea14664"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="5" r:id="Rfde7d98405524597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="6" r:id="Rec382f528a2f4457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="7" r:id="R3e01691048274d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5988a6c782204d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R2b000484bc244702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly" sheetId="3" r:id="R00bdb899987e4bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="4" r:id="R3714826963614182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="5" r:id="Rfb7a9051512846aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Invoices" sheetId="6" r:id="R743c7d87ed5844c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="7" r:id="R850b6c8fd31c45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="8" r:id="Rda7f451816cc4d62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +28,7 @@
     <x:numFmt numFmtId="204" formatCode="0.0%"/>
     <x:numFmt numFmtId="205" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -75,6 +76,16 @@
       <x:color rgb="FF111111"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0759E6"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF087A55"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="4">
     <x:fill>
@@ -115,7 +126,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -182,17 +193,45 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="204" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="205" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="3">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB91C1C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -236,7 +275,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Weekly cash before financing (USD)</a:t>
+              <a:t>26-week funded cash (USD)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -264,25 +303,14 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Ending cash</c:v>
+            <c:v>Funded cash</c:v>
           </c:tx>
-          <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="17324D"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
-              <a:solidFill>
-                <a:srgbClr val="17324D"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Summary'!$C$17:$C$29</c:f>
+              <c:f>'Summary'!$C$17:$C$42</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -290,7 +318,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Summary'!$D$17:$D$29</c:f>
+              <c:f>'Summary'!$D$17:$D$42</c:f>
               <c:numCache>
                 <c:formatCode>$#,##0;($#,##0);"-"</c:formatCode>
                 <c:ptCount val="0"/>
@@ -305,23 +333,12 @@
           <c:tx>
             <c:v>Minimum floor</c:v>
           </c:tx>
-          <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="15A6AC"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
-              <a:solidFill>
-                <a:srgbClr val="15A6AC"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Summary'!$C$17:$C$29</c:f>
+              <c:f>'Summary'!$C$17:$C$42</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -329,7 +346,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Summary'!$E$17:$E$29</c:f>
+              <c:f>'Summary'!$E$17:$E$42</c:f>
               <c:numCache>
                 <c:formatCode>$#,##0;($#,##0);"-"</c:formatCode>
                 <c:ptCount val="0"/>
@@ -395,7 +412,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="$0,&quot;k&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="$0.0,,&quot;M&quot;" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:txPr>
@@ -458,7 +475,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff51185a279641de"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R272f2dc0ff0845dd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -700,7 +717,7 @@
       <x:c r="A2" s="1"/>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="2" t="str">
-        <x:v>13-week liquidity and working capital</x:v>
+        <x:v>26-week liquidity and funding</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="1"/>
@@ -798,14 +815,14 @@
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1"/>
       <x:c r="C7" s="5" t="str">
-        <x:v>Lowest weekly cash</x:v>
+        <x:v>Lowest funded cash</x:v>
       </x:c>
       <x:c r="D7" s="18" t="n">
-        <x:f>MIN('Weekly'!D18:P18)</x:f>
-        <x:v>119000</x:v>
+        <x:f>MIN('Weekly'!D27:AC27)</x:f>
+        <x:v>178980.76923076922</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>Before financing</x:v>
+        <x:v>After facility flows</x:v>
       </x:c>
       <x:c r="F7" s="1"/>
       <x:c r="G7" s="1"/>
@@ -822,14 +839,14 @@
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1"/>
       <x:c r="C8" s="5" t="str">
-        <x:v>Funding needed to maintain floor</x:v>
+        <x:v>Peak facility debt</x:v>
       </x:c>
       <x:c r="D8" s="18" t="n">
-        <x:f>MAX('Weekly'!D20:P20)</x:f>
+        <x:f>MAX('Weekly'!D26:AC26)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>Peak cumulative gap</x:v>
+        <x:v>Assumed $200k limit</x:v>
       </x:c>
       <x:c r="F8" s="1"/>
       <x:c r="G8" s="1"/>
@@ -849,11 +866,11 @@
         <x:v>Ending cash</x:v>
       </x:c>
       <x:c r="D9" s="18" t="n">
-        <x:f>'Weekly'!P18</x:f>
-        <x:v>149000</x:v>
+        <x:f>'Weekly'!AC27</x:f>
+        <x:v>1160500.0000000005</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Week 13</x:v>
+        <x:v>Week 26</x:v>
       </x:c>
       <x:c r="F9" s="1"/>
       <x:c r="G9" s="1"/>
@@ -873,8 +890,8 @@
         <x:v>Open invoices beyond horizon</x:v>
       </x:c>
       <x:c r="D10" s="18" t="n">
-        <x:f>SUMIFS('Invoices'!F7:F32,'Invoices'!H7:H32,"&gt;13")</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Invoices'!F7:F32,'Invoices'!H7:H32,"&gt;26")+SUMIFS('New Invoices'!E7:E32,'New Invoices'!F7:F32,"&gt;26")</x:f>
+        <x:v>184000</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
         <x:v>Carry-forward, not lost</x:v>
@@ -897,7 +914,7 @@
         <x:v>Capex beyond horizon</x:v>
       </x:c>
       <x:c r="D11" s="18" t="n">
-        <x:f>IF('Assumptions'!D18&gt;13,'Assumptions'!G16,0)</x:f>
+        <x:f>IF('Assumptions'!D18&gt;26,'Assumptions'!G16,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
@@ -941,8 +958,13 @@
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
+      <x:c r="C13" s="1" t="str">
+        <x:v>Residual funding shortfall</x:v>
+      </x:c>
+      <x:c r="D13" s="46" t="n">
+        <x:f>MAX('Weekly'!D29:AC29)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E13" s="1"/>
       <x:c r="F13" s="1"/>
       <x:c r="G13" s="1"/>
@@ -958,8 +980,13 @@
     <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1"/>
-      <x:c r="D14" s="1"/>
+      <x:c r="C14" s="1" t="str">
+        <x:v>Unfunded minimum cash</x:v>
+      </x:c>
+      <x:c r="D14" s="46" t="n">
+        <x:f>MIN('Weekly'!D30:AC30)</x:f>
+        <x:v>179000</x:v>
+      </x:c>
       <x:c r="E14" s="1"/>
       <x:c r="F14" s="1"/>
       <x:c r="G14" s="1"/>
@@ -996,7 +1023,7 @@
         <x:v>Week</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>Ending cash</x:v>
+        <x:v>Funded cash</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
         <x:v>Minimum floor</x:v>
@@ -1019,11 +1046,11 @@
         <x:v>W1</x:v>
       </x:c>
       <x:c r="D17" s="18" t="n">
-        <x:f>'Weekly'!D18</x:f>
-        <x:v>179000</x:v>
+        <x:f>'Weekly'!D27</x:f>
+        <x:v>178980.76923076922</x:v>
       </x:c>
       <x:c r="E17" s="18" t="n">
-        <x:f>'Weekly'!D19</x:f>
+        <x:f>'Weekly'!D28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F17" s="1"/>
@@ -1044,11 +1071,11 @@
         <x:v>W2</x:v>
       </x:c>
       <x:c r="D18" s="18" t="n">
-        <x:f>'Weekly'!E18</x:f>
-        <x:v>190000</x:v>
+        <x:f>'Weekly'!E27</x:f>
+        <x:v>189961.53846153844</x:v>
       </x:c>
       <x:c r="E18" s="18" t="n">
-        <x:f>'Weekly'!E19</x:f>
+        <x:f>'Weekly'!E28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F18" s="1"/>
@@ -1069,11 +1096,11 @@
         <x:v>W3</x:v>
       </x:c>
       <x:c r="D19" s="18" t="n">
-        <x:f>'Weekly'!F18</x:f>
-        <x:v>189000</x:v>
+        <x:f>'Weekly'!F27</x:f>
+        <x:v>280942.3076923077</x:v>
       </x:c>
       <x:c r="E19" s="18" t="n">
-        <x:f>'Weekly'!F19</x:f>
+        <x:f>'Weekly'!F28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F19" s="1"/>
@@ -1094,11 +1121,11 @@
         <x:v>W4</x:v>
       </x:c>
       <x:c r="D20" s="18" t="n">
-        <x:f>'Weekly'!G18</x:f>
-        <x:v>200000</x:v>
+        <x:f>'Weekly'!G27</x:f>
+        <x:v>383923.07692307694</x:v>
       </x:c>
       <x:c r="E20" s="18" t="n">
-        <x:f>'Weekly'!G19</x:f>
+        <x:f>'Weekly'!G28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F20" s="1"/>
@@ -1119,11 +1146,11 @@
         <x:v>W5</x:v>
       </x:c>
       <x:c r="D21" s="18" t="n">
-        <x:f>'Weekly'!H18</x:f>
-        <x:v>199000</x:v>
+        <x:f>'Weekly'!H27</x:f>
+        <x:v>474903.8461538462</x:v>
       </x:c>
       <x:c r="E21" s="18" t="n">
-        <x:f>'Weekly'!H19</x:f>
+        <x:f>'Weekly'!H28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F21" s="1"/>
@@ -1144,11 +1171,11 @@
         <x:v>W6</x:v>
       </x:c>
       <x:c r="D22" s="18" t="n">
-        <x:f>'Weekly'!I18</x:f>
-        <x:v>120000</x:v>
+        <x:f>'Weekly'!I27</x:f>
+        <x:v>487884.61538461543</x:v>
       </x:c>
       <x:c r="E22" s="18" t="n">
-        <x:f>'Weekly'!I19</x:f>
+        <x:f>'Weekly'!I28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F22" s="1"/>
@@ -1169,11 +1196,11 @@
         <x:v>W7</x:v>
       </x:c>
       <x:c r="D23" s="18" t="n">
-        <x:f>'Weekly'!J18</x:f>
-        <x:v>119000</x:v>
+        <x:f>'Weekly'!J27</x:f>
+        <x:v>578865.3846153847</x:v>
       </x:c>
       <x:c r="E23" s="18" t="n">
-        <x:f>'Weekly'!J19</x:f>
+        <x:f>'Weekly'!J28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F23" s="1"/>
@@ -1194,11 +1221,11 @@
         <x:v>W8</x:v>
       </x:c>
       <x:c r="D24" s="18" t="n">
-        <x:f>'Weekly'!K18</x:f>
-        <x:v>130000</x:v>
+        <x:f>'Weekly'!K27</x:f>
+        <x:v>681846.153846154</x:v>
       </x:c>
       <x:c r="E24" s="18" t="n">
-        <x:f>'Weekly'!K19</x:f>
+        <x:f>'Weekly'!K28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F24" s="1"/>
@@ -1219,17 +1246,17 @@
         <x:v>W9</x:v>
       </x:c>
       <x:c r="D25" s="18" t="n">
-        <x:f>'Weekly'!L18</x:f>
-        <x:v>129000</x:v>
+        <x:f>'Weekly'!L27</x:f>
+        <x:v>772826.9230769232</x:v>
       </x:c>
       <x:c r="E25" s="18" t="n">
-        <x:f>'Weekly'!L19</x:f>
+        <x:f>'Weekly'!L28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F25" s="1"/>
       <x:c r="G25" s="1"/>
       <x:c r="H25" s="5" t="str">
-        <x:v>Accelerate eligible collections with consent. Defer capex only after review.</x:v>
+        <x:v>Facility terms are hypothetical. Deferred capex is paid in week 14.</x:v>
       </x:c>
       <x:c r="I25" s="5"/>
       <x:c r="J25" s="5"/>
@@ -1246,11 +1273,11 @@
         <x:v>W10</x:v>
       </x:c>
       <x:c r="D26" s="18" t="n">
-        <x:f>'Weekly'!M18</x:f>
-        <x:v>140000</x:v>
+        <x:f>'Weekly'!M27</x:f>
+        <x:v>875807.6923076925</x:v>
       </x:c>
       <x:c r="E26" s="18" t="n">
-        <x:f>'Weekly'!M19</x:f>
+        <x:f>'Weekly'!M28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F26" s="1"/>
@@ -1271,11 +1298,11 @@
         <x:v>W11</x:v>
       </x:c>
       <x:c r="D27" s="18" t="n">
-        <x:f>'Weekly'!N18</x:f>
-        <x:v>139000</x:v>
+        <x:f>'Weekly'!N27</x:f>
+        <x:v>966788.4615384617</x:v>
       </x:c>
       <x:c r="E27" s="18" t="n">
-        <x:f>'Weekly'!N19</x:f>
+        <x:f>'Weekly'!N28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F27" s="1"/>
@@ -1296,11 +1323,11 @@
         <x:v>W12</x:v>
       </x:c>
       <x:c r="D28" s="18" t="n">
-        <x:f>'Weekly'!O18</x:f>
-        <x:v>150000</x:v>
+        <x:f>'Weekly'!O27</x:f>
+        <x:v>1069769.230769231</x:v>
       </x:c>
       <x:c r="E28" s="18" t="n">
-        <x:f>'Weekly'!O19</x:f>
+        <x:f>'Weekly'!O28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F28" s="1"/>
@@ -1321,11 +1348,11 @@
         <x:v>W13</x:v>
       </x:c>
       <x:c r="D29" s="18" t="n">
-        <x:f>'Weekly'!P18</x:f>
-        <x:v>149000</x:v>
+        <x:f>'Weekly'!P27</x:f>
+        <x:v>1160750.0000000002</x:v>
       </x:c>
       <x:c r="E29" s="18" t="n">
-        <x:f>'Weekly'!P19</x:f>
+        <x:f>'Weekly'!P28</x:f>
         <x:v>100000</x:v>
       </x:c>
       <x:c r="F29" s="1"/>
@@ -1342,9 +1369,17 @@
     <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1"/>
-      <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
+      <x:c r="C30" s="1" t="str">
+        <x:v>W14</x:v>
+      </x:c>
+      <x:c r="D30" s="46" t="n">
+        <x:f>'Weekly'!Q27</x:f>
+        <x:v>1160730.7692307695</x:v>
+      </x:c>
+      <x:c r="E30" s="46" t="n">
+        <x:f>'Weekly'!Q28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F30" s="1"/>
       <x:c r="G30" s="1"/>
       <x:c r="H30" s="1"/>
@@ -1359,9 +1394,17 @@
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
+      <x:c r="C31" s="1" t="str">
+        <x:v>W15</x:v>
+      </x:c>
+      <x:c r="D31" s="46" t="n">
+        <x:f>'Weekly'!R27</x:f>
+        <x:v>1160711.5384615387</x:v>
+      </x:c>
+      <x:c r="E31" s="46" t="n">
+        <x:f>'Weekly'!R28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F31" s="1"/>
       <x:c r="G31" s="1"/>
       <x:c r="H31" s="1"/>
@@ -1376,9 +1419,17 @@
     <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1"/>
-      <x:c r="C32" s="1"/>
-      <x:c r="D32" s="1"/>
-      <x:c r="E32" s="1"/>
+      <x:c r="C32" s="1" t="str">
+        <x:v>W16</x:v>
+      </x:c>
+      <x:c r="D32" s="46" t="n">
+        <x:f>'Weekly'!S27</x:f>
+        <x:v>1160692.307692308</x:v>
+      </x:c>
+      <x:c r="E32" s="46" t="n">
+        <x:f>'Weekly'!S28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F32" s="1"/>
       <x:c r="G32" s="1"/>
       <x:c r="H32" s="1"/>
@@ -1393,9 +1444,17 @@
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1"/>
-      <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
+      <x:c r="C33" s="1" t="str">
+        <x:v>W17</x:v>
+      </x:c>
+      <x:c r="D33" s="46" t="n">
+        <x:f>'Weekly'!T27</x:f>
+        <x:v>1160673.0769230772</x:v>
+      </x:c>
+      <x:c r="E33" s="46" t="n">
+        <x:f>'Weekly'!T28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F33" s="1"/>
       <x:c r="G33" s="1"/>
       <x:c r="H33" s="1"/>
@@ -1410,9 +1469,17 @@
     <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1"/>
-      <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
+      <x:c r="C34" s="1" t="str">
+        <x:v>W18</x:v>
+      </x:c>
+      <x:c r="D34" s="46" t="n">
+        <x:f>'Weekly'!U27</x:f>
+        <x:v>1160653.8461538465</x:v>
+      </x:c>
+      <x:c r="E34" s="46" t="n">
+        <x:f>'Weekly'!U28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F34" s="1"/>
       <x:c r="G34" s="1"/>
       <x:c r="H34" s="1"/>
@@ -1427,9 +1494,17 @@
     <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1"/>
-      <x:c r="C35" s="1"/>
-      <x:c r="D35" s="1"/>
-      <x:c r="E35" s="1"/>
+      <x:c r="C35" s="1" t="str">
+        <x:v>W19</x:v>
+      </x:c>
+      <x:c r="D35" s="46" t="n">
+        <x:f>'Weekly'!V27</x:f>
+        <x:v>1160634.6153846157</x:v>
+      </x:c>
+      <x:c r="E35" s="46" t="n">
+        <x:f>'Weekly'!V28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F35" s="1"/>
       <x:c r="G35" s="1"/>
       <x:c r="H35" s="1"/>
@@ -1444,9 +1519,17 @@
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
+      <x:c r="C36" s="1" t="str">
+        <x:v>W20</x:v>
+      </x:c>
+      <x:c r="D36" s="46" t="n">
+        <x:f>'Weekly'!W27</x:f>
+        <x:v>1160615.384615385</x:v>
+      </x:c>
+      <x:c r="E36" s="46" t="n">
+        <x:f>'Weekly'!W28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F36" s="1"/>
       <x:c r="G36" s="1"/>
       <x:c r="H36" s="1"/>
@@ -1461,9 +1544,17 @@
     <x:row r="37" ht="22" customHeight="1">
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1"/>
-      <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-      <x:c r="E37" s="1"/>
+      <x:c r="C37" s="1" t="str">
+        <x:v>W21</x:v>
+      </x:c>
+      <x:c r="D37" s="46" t="n">
+        <x:f>'Weekly'!X27</x:f>
+        <x:v>1160596.1538461542</x:v>
+      </x:c>
+      <x:c r="E37" s="46" t="n">
+        <x:f>'Weekly'!X28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F37" s="1"/>
       <x:c r="G37" s="1"/>
       <x:c r="H37" s="1"/>
@@ -1478,9 +1569,17 @@
     <x:row r="38" ht="22" customHeight="1">
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1"/>
-      <x:c r="C38" s="1"/>
-      <x:c r="D38" s="1"/>
-      <x:c r="E38" s="1"/>
+      <x:c r="C38" s="1" t="str">
+        <x:v>W22</x:v>
+      </x:c>
+      <x:c r="D38" s="46" t="n">
+        <x:f>'Weekly'!Y27</x:f>
+        <x:v>1160576.9230769235</x:v>
+      </x:c>
+      <x:c r="E38" s="46" t="n">
+        <x:f>'Weekly'!Y28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F38" s="1"/>
       <x:c r="G38" s="1"/>
       <x:c r="H38" s="1"/>
@@ -1495,9 +1594,17 @@
     <x:row r="39" ht="22" customHeight="1">
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1"/>
-      <x:c r="C39" s="1"/>
-      <x:c r="D39" s="1"/>
-      <x:c r="E39" s="1"/>
+      <x:c r="C39" s="1" t="str">
+        <x:v>W23</x:v>
+      </x:c>
+      <x:c r="D39" s="46" t="n">
+        <x:f>'Weekly'!Z27</x:f>
+        <x:v>1160557.6923076927</x:v>
+      </x:c>
+      <x:c r="E39" s="46" t="n">
+        <x:f>'Weekly'!Z28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F39" s="1"/>
       <x:c r="G39" s="1"/>
       <x:c r="H39" s="1"/>
@@ -1512,9 +1619,17 @@
     <x:row r="40" ht="22" customHeight="1">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1"/>
-      <x:c r="C40" s="1"/>
-      <x:c r="D40" s="1"/>
-      <x:c r="E40" s="1"/>
+      <x:c r="C40" s="1" t="str">
+        <x:v>W24</x:v>
+      </x:c>
+      <x:c r="D40" s="46" t="n">
+        <x:f>'Weekly'!AA27</x:f>
+        <x:v>1160538.461538462</x:v>
+      </x:c>
+      <x:c r="E40" s="46" t="n">
+        <x:f>'Weekly'!AA28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F40" s="1"/>
       <x:c r="G40" s="1"/>
       <x:c r="H40" s="1"/>
@@ -1529,9 +1644,17 @@
     <x:row r="41" ht="22" customHeight="1">
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1"/>
-      <x:c r="C41" s="1"/>
-      <x:c r="D41" s="1"/>
-      <x:c r="E41" s="1"/>
+      <x:c r="C41" s="1" t="str">
+        <x:v>W25</x:v>
+      </x:c>
+      <x:c r="D41" s="46" t="n">
+        <x:f>'Weekly'!AB27</x:f>
+        <x:v>1160519.2307692312</x:v>
+      </x:c>
+      <x:c r="E41" s="46" t="n">
+        <x:f>'Weekly'!AB28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F41" s="1"/>
       <x:c r="G41" s="1"/>
       <x:c r="H41" s="1"/>
@@ -1546,9 +1669,17 @@
     <x:row r="42" ht="22" customHeight="1">
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1"/>
-      <x:c r="C42" s="1"/>
-      <x:c r="D42" s="1"/>
-      <x:c r="E42" s="1"/>
+      <x:c r="C42" s="1" t="str">
+        <x:v>W26</x:v>
+      </x:c>
+      <x:c r="D42" s="46" t="n">
+        <x:f>'Weekly'!AC27</x:f>
+        <x:v>1160500.0000000005</x:v>
+      </x:c>
+      <x:c r="E42" s="46" t="n">
+        <x:f>'Weekly'!AC28</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="F42" s="1"/>
       <x:c r="G42" s="1"/>
       <x:c r="H42" s="1"/>
@@ -1957,7 +2088,7 @@
     <x:mergeCell ref="H25:O27"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5aaac6d1e6cd4122"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a77f0a0b0d49d4"/>
 </x:worksheet>
 </file>
 
@@ -1970,9 +2101,9 @@
     <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
@@ -2126,7 +2257,7 @@
       <x:c r="F9" s="5" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="n">
+      <x:c r="G9" s="31" t="n">
         <x:v>180000</x:v>
       </x:c>
       <x:c r="H9" s="5" t="str">
@@ -2150,7 +2281,7 @@
       <x:c r="F10" s="5" t="str">
         <x:v>Minimum cash</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="n">
+      <x:c r="G10" s="31" t="n">
         <x:v>100000</x:v>
       </x:c>
       <x:c r="H10" s="5" t="str">
@@ -2174,7 +2305,7 @@
       <x:c r="F11" s="5" t="str">
         <x:v>Weekly direct cash sales</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="n">
+      <x:c r="G11" s="31" t="n">
         <x:v>20000</x:v>
       </x:c>
       <x:c r="H11" s="5" t="str">
@@ -2194,7 +2325,7 @@
       <x:c r="F12" s="5" t="str">
         <x:v>Weekly payroll</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="n">
+      <x:c r="G12" s="31" t="n">
         <x:v>45000</x:v>
       </x:c>
       <x:c r="H12" s="5" t="str">
@@ -2219,7 +2350,7 @@
       <x:c r="F13" s="5" t="str">
         <x:v>Weekly fuel</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="n">
+      <x:c r="G13" s="31" t="n">
         <x:v>20000</x:v>
       </x:c>
       <x:c r="H13" s="5" t="str">
@@ -2243,7 +2374,7 @@
       <x:c r="F14" s="5" t="str">
         <x:v>Weekly supplier AP</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="n">
+      <x:c r="G14" s="31" t="n">
         <x:v>35000</x:v>
       </x:c>
       <x:c r="H14" s="5" t="str">
@@ -2267,7 +2398,7 @@
       <x:c r="F15" s="5" t="str">
         <x:v>Weekly lease payments</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="n">
+      <x:c r="G15" s="31" t="n">
         <x:v>12000</x:v>
       </x:c>
       <x:c r="H15" s="5" t="str">
@@ -2291,7 +2422,7 @@
       <x:c r="F16" s="5" t="str">
         <x:v>One-time capex</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="n">
+      <x:c r="G16" s="31" t="n">
         <x:v>90000</x:v>
       </x:c>
       <x:c r="H16" s="5" t="str">
@@ -2435,7 +2566,7 @@
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1"/>
       <x:c r="C25" s="5" t="str">
-        <x:v>Week 1 starts 5-Oct-2026. No financing availability is assumed.</x:v>
+        <x:v>Week 1 starts 5-Oct-2026. Facility availability is a hypothetical input.</x:v>
       </x:c>
       <x:c r="D25" s="5"/>
       <x:c r="E25" s="5"/>
@@ -2561,142 +2692,233 @@
       <x:c r="K33" s="1"/>
       <x:c r="L33" s="1"/>
     </x:row>
-    <x:row r="34" ht="22" customHeight="1">
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1"/>
       <x:c r="C34" s="1"/>
       <x:c r="D34" s="1"/>
       <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-      <x:c r="I34" s="1"/>
+      <x:c r="F34" s="14" t="str">
+        <x:v>Expanded driver</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="H34" s="14" t="str">
+        <x:v>Synthetic assumption</x:v>
+      </x:c>
+      <x:c r="I34" s="45" t="str">
+        <x:v>Validated value</x:v>
+      </x:c>
       <x:c r="J34" s="1"/>
       <x:c r="K34" s="1"/>
       <x:c r="L34" s="1"/>
     </x:row>
-    <x:row r="35" ht="22" customHeight="1">
+    <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1"/>
       <x:c r="C35" s="1"/>
       <x:c r="D35" s="1"/>
       <x:c r="E35" s="1"/>
-      <x:c r="F35" s="1"/>
-      <x:c r="G35" s="1"/>
-      <x:c r="H35" s="1"/>
-      <x:c r="I35" s="1"/>
+      <x:c r="F35" s="5" t="str">
+        <x:v>Facility limit</x:v>
+      </x:c>
+      <x:c r="G35" s="31" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="H35" s="5" t="str">
+        <x:v>Hypothetical undrawn revolver; not approved</x:v>
+      </x:c>
+      <x:c r="I35" s="29" t="n">
+        <x:f>IF(AND(ISNUMBER(G35),G35&gt;=0),G35,NA())</x:f>
+        <x:v>200000</x:v>
+      </x:c>
       <x:c r="J35" s="1"/>
       <x:c r="K35" s="1"/>
       <x:c r="L35" s="1"/>
     </x:row>
-    <x:row r="36" ht="22" customHeight="1">
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1"/>
       <x:c r="C36" s="1"/>
       <x:c r="D36" s="1"/>
       <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-      <x:c r="H36" s="1"/>
-      <x:c r="I36" s="1"/>
+      <x:c r="F36" s="5" t="str">
+        <x:v>Annual facility rate</x:v>
+      </x:c>
+      <x:c r="G36" s="41" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="H36" s="5" t="str">
+        <x:v>Opening weekly debt basis</x:v>
+      </x:c>
+      <x:c r="I36" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(G36),G36&gt;=0,G36&lt;=1),G36,NA())</x:f>
+        <x:v>0.09</x:v>
+      </x:c>
       <x:c r="J36" s="1"/>
       <x:c r="K36" s="1"/>
       <x:c r="L36" s="1"/>
     </x:row>
-    <x:row r="37" ht="22" customHeight="1">
+    <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1"/>
       <x:c r="C37" s="1"/>
       <x:c r="D37" s="1"/>
       <x:c r="E37" s="1"/>
-      <x:c r="F37" s="1"/>
-      <x:c r="G37" s="1"/>
-      <x:c r="H37" s="1"/>
-      <x:c r="I37" s="1"/>
+      <x:c r="F37" s="5" t="str">
+        <x:v>Commitment fee</x:v>
+      </x:c>
+      <x:c r="G37" s="41" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="H37" s="5" t="str">
+        <x:v>Annual on unused opening commitment</x:v>
+      </x:c>
+      <x:c r="I37" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(G37),G37&gt;=0,G37&lt;=1),G37,NA())</x:f>
+        <x:v>0.005</x:v>
+      </x:c>
       <x:c r="J37" s="1"/>
       <x:c r="K37" s="1"/>
       <x:c r="L37" s="1"/>
     </x:row>
-    <x:row r="38" ht="22" customHeight="1">
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1"/>
       <x:c r="C38" s="1"/>
       <x:c r="D38" s="1"/>
       <x:c r="E38" s="1"/>
-      <x:c r="F38" s="1"/>
-      <x:c r="G38" s="1"/>
-      <x:c r="H38" s="1"/>
-      <x:c r="I38" s="1"/>
+      <x:c r="F38" s="5" t="str">
+        <x:v>Opening facility debt</x:v>
+      </x:c>
+      <x:c r="G38" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="5" t="str">
+        <x:v>Week 1</x:v>
+      </x:c>
+      <x:c r="I38" s="29" t="n">
+        <x:f>IF(AND(ISNUMBER(G38),G38&gt;=0,ISNUMBER(G35),G38&lt;=G35),G38,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J38" s="1"/>
       <x:c r="K38" s="1"/>
       <x:c r="L38" s="1"/>
     </x:row>
-    <x:row r="39" ht="22" customHeight="1">
+    <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1"/>
       <x:c r="C39" s="1"/>
       <x:c r="D39" s="1"/>
       <x:c r="E39" s="1"/>
-      <x:c r="F39" s="1"/>
-      <x:c r="G39" s="1"/>
-      <x:c r="H39" s="1"/>
-      <x:c r="I39" s="1"/>
+      <x:c r="F39" s="5" t="str">
+        <x:v>Weekly credit billings</x:v>
+      </x:c>
+      <x:c r="G39" s="31" t="n">
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="H39" s="5" t="str">
+        <x:v>Separate from opening AR and cash sales</x:v>
+      </x:c>
+      <x:c r="I39" s="29" t="n">
+        <x:f>IF(AND(ISNUMBER(G39),G39&gt;=0),G39,NA())</x:f>
+        <x:v>92000</x:v>
+      </x:c>
       <x:c r="J39" s="1"/>
       <x:c r="K39" s="1"/>
       <x:c r="L39" s="1"/>
     </x:row>
-    <x:row r="40" ht="22" customHeight="1">
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1"/>
       <x:c r="C40" s="1"/>
       <x:c r="D40" s="1"/>
       <x:c r="E40" s="1"/>
-      <x:c r="F40" s="1"/>
-      <x:c r="G40" s="1"/>
-      <x:c r="H40" s="1"/>
-      <x:c r="I40" s="1"/>
+      <x:c r="F40" s="5" t="str">
+        <x:v>Credit collection lag weeks</x:v>
+      </x:c>
+      <x:c r="G40" s="42" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H40" s="5" t="str">
+        <x:v>Active scenario adds receipt delay</x:v>
+      </x:c>
+      <x:c r="I40" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G40),G40&gt;=0,MOD(G40,1)=0),G40,NA())</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="J40" s="1"/>
       <x:c r="K40" s="1"/>
       <x:c r="L40" s="1"/>
     </x:row>
-    <x:row r="41" ht="22" customHeight="1">
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1"/>
       <x:c r="C41" s="1"/>
       <x:c r="D41" s="1"/>
       <x:c r="E41" s="1"/>
-      <x:c r="F41" s="1"/>
-      <x:c r="G41" s="1"/>
-      <x:c r="H41" s="1"/>
-      <x:c r="I41" s="1"/>
+      <x:c r="F41" s="5" t="str">
+        <x:v>Forecast weeks</x:v>
+      </x:c>
+      <x:c r="G41" s="43" t="n">
+        <x:f>26</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H41" s="5" t="str">
+        <x:v>Fixed 26-week build, not an editable horizon</x:v>
+      </x:c>
+      <x:c r="I41" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G41),G41&gt;=0),G41,NA())</x:f>
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="J41" s="1"/>
       <x:c r="K41" s="1"/>
       <x:c r="L41" s="1"/>
     </x:row>
-    <x:row r="42" ht="22" customHeight="1">
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1"/>
       <x:c r="C42" s="1"/>
       <x:c r="D42" s="1"/>
       <x:c r="E42" s="1"/>
-      <x:c r="F42" s="1"/>
-      <x:c r="G42" s="1"/>
-      <x:c r="H42" s="1"/>
-      <x:c r="I42" s="1"/>
+      <x:c r="F42" s="5" t="str">
+        <x:v>Auto-repayment</x:v>
+      </x:c>
+      <x:c r="G42" s="42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="5" t="str">
+        <x:v>Repay excess above floor</x:v>
+      </x:c>
+      <x:c r="I42" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G42),G42&gt;=0,G42&lt;=1,MOD(G42,1)=0),G42,NA())</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="J42" s="1"/>
       <x:c r="K42" s="1"/>
       <x:c r="L42" s="1"/>
     </x:row>
-    <x:row r="43" ht="22" customHeight="1">
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1"/>
       <x:c r="C43" s="1"/>
       <x:c r="D43" s="1"/>
       <x:c r="E43" s="1"/>
-      <x:c r="F43" s="1"/>
-      <x:c r="G43" s="1"/>
-      <x:c r="H43" s="1"/>
-      <x:c r="I43" s="1"/>
+      <x:c r="F43" s="5" t="str">
+        <x:v>Cash floor (linked)</x:v>
+      </x:c>
+      <x:c r="G43" s="32" t="n">
+        <x:f>G10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="H43" s="5" t="str">
+        <x:v>Linked to the minimum cash input above</x:v>
+      </x:c>
+      <x:c r="I43" s="29" t="n">
+        <x:f>IF(AND(ISNUMBER(G43),G43&gt;=0),G43,NA())</x:f>
+        <x:v>100000</x:v>
+      </x:c>
       <x:c r="J43" s="1"/>
       <x:c r="K43" s="1"/>
       <x:c r="L43" s="1"/>
@@ -3030,7 +3252,7 @@
   <x:cols>
     <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
@@ -3044,6 +3266,19 @@
     <x:col min="14" max="14" width="17" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="17" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="17" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="17" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="17" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="17" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="17" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="17" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="17" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="17" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="17" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="17" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="17" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="17" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="17" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -3168,6 +3403,45 @@
       <x:c r="P5" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="Q5" s="34" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="R5" s="34" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S5" s="34" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="T5" s="34" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="U5" s="34" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="V5" s="34" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="W5" s="34" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="X5" s="34" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Y5" s="34" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Z5" s="34" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="AA5" s="34" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="AB5" s="34" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AC5" s="34" t="n">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="1"/>
@@ -3212,71 +3486,162 @@
       <x:c r="P6" s="27" t="d">
         <x:v>2026-12-28T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="Q6" s="35" t="d">
+        <x:v>2027-01-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="R6" s="35" t="d">
+        <x:v>2027-01-11T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="S6" s="35" t="d">
+        <x:v>2027-01-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="T6" s="35" t="d">
+        <x:v>2027-01-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="U6" s="35" t="d">
+        <x:v>2027-02-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="V6" s="35" t="d">
+        <x:v>2027-02-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="W6" s="35" t="d">
+        <x:v>2027-02-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="X6" s="35" t="d">
+        <x:v>2027-02-22T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="Y6" s="35" t="d">
+        <x:v>2027-03-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="Z6" s="35" t="d">
+        <x:v>2027-03-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AA6" s="35" t="d">
+        <x:v>2027-03-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AB6" s="35" t="d">
+        <x:v>2027-03-22T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AC6" s="35" t="d">
+        <x:v>2027-03-29T00:00:00.000Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1"/>
       <x:c r="C7" s="1" t="str">
-        <x:v>Opening cash</x:v>
+        <x:v>Opening funded cash</x:v>
       </x:c>
       <x:c r="D7" s="28" t="n">
         <x:f>'Assumptions'!G9</x:f>
         <x:v>180000</x:v>
       </x:c>
       <x:c r="E7" s="29" t="n">
-        <x:f>D18</x:f>
-        <x:v>179000</x:v>
+        <x:f>D27</x:f>
+        <x:v>178980.76923076922</x:v>
       </x:c>
       <x:c r="F7" s="29" t="n">
-        <x:f>E18</x:f>
-        <x:v>190000</x:v>
+        <x:f>E27</x:f>
+        <x:v>189961.53846153844</x:v>
       </x:c>
       <x:c r="G7" s="29" t="n">
-        <x:f>F18</x:f>
-        <x:v>189000</x:v>
+        <x:f>F27</x:f>
+        <x:v>280942.3076923077</x:v>
       </x:c>
       <x:c r="H7" s="29" t="n">
-        <x:f>G18</x:f>
-        <x:v>200000</x:v>
+        <x:f>G27</x:f>
+        <x:v>383923.07692307694</x:v>
       </x:c>
       <x:c r="I7" s="29" t="n">
-        <x:f>H18</x:f>
-        <x:v>199000</x:v>
+        <x:f>H27</x:f>
+        <x:v>474903.8461538462</x:v>
       </x:c>
       <x:c r="J7" s="29" t="n">
-        <x:f>I18</x:f>
-        <x:v>120000</x:v>
+        <x:f>I27</x:f>
+        <x:v>487884.61538461543</x:v>
       </x:c>
       <x:c r="K7" s="29" t="n">
-        <x:f>J18</x:f>
-        <x:v>119000</x:v>
+        <x:f>J27</x:f>
+        <x:v>578865.3846153847</x:v>
       </x:c>
       <x:c r="L7" s="29" t="n">
-        <x:f>K18</x:f>
-        <x:v>130000</x:v>
+        <x:f>K27</x:f>
+        <x:v>681846.153846154</x:v>
       </x:c>
       <x:c r="M7" s="29" t="n">
-        <x:f>L18</x:f>
-        <x:v>129000</x:v>
+        <x:f>L27</x:f>
+        <x:v>772826.9230769232</x:v>
       </x:c>
       <x:c r="N7" s="29" t="n">
-        <x:f>M18</x:f>
-        <x:v>140000</x:v>
+        <x:f>M27</x:f>
+        <x:v>875807.6923076925</x:v>
       </x:c>
       <x:c r="O7" s="29" t="n">
-        <x:f>N18</x:f>
-        <x:v>139000</x:v>
+        <x:f>N27</x:f>
+        <x:v>966788.4615384617</x:v>
       </x:c>
       <x:c r="P7" s="29" t="n">
-        <x:f>O18</x:f>
-        <x:v>150000</x:v>
+        <x:f>O27</x:f>
+        <x:v>1069769.230769231</x:v>
+      </x:c>
+      <x:c r="Q7" s="37" t="n">
+        <x:f>P27</x:f>
+        <x:v>1160750.0000000002</x:v>
+      </x:c>
+      <x:c r="R7" s="37" t="n">
+        <x:f>Q27</x:f>
+        <x:v>1160730.7692307695</x:v>
+      </x:c>
+      <x:c r="S7" s="37" t="n">
+        <x:f>R27</x:f>
+        <x:v>1160711.5384615387</x:v>
+      </x:c>
+      <x:c r="T7" s="37" t="n">
+        <x:f>S27</x:f>
+        <x:v>1160692.307692308</x:v>
+      </x:c>
+      <x:c r="U7" s="37" t="n">
+        <x:f>T27</x:f>
+        <x:v>1160673.0769230772</x:v>
+      </x:c>
+      <x:c r="V7" s="37" t="n">
+        <x:f>U27</x:f>
+        <x:v>1160653.8461538465</x:v>
+      </x:c>
+      <x:c r="W7" s="37" t="n">
+        <x:f>V27</x:f>
+        <x:v>1160634.6153846157</x:v>
+      </x:c>
+      <x:c r="X7" s="37" t="n">
+        <x:f>W27</x:f>
+        <x:v>1160615.384615385</x:v>
+      </x:c>
+      <x:c r="Y7" s="37" t="n">
+        <x:f>X27</x:f>
+        <x:v>1160596.1538461542</x:v>
+      </x:c>
+      <x:c r="Z7" s="37" t="n">
+        <x:f>Y27</x:f>
+        <x:v>1160576.9230769235</x:v>
+      </x:c>
+      <x:c r="AA7" s="37" t="n">
+        <x:f>Z27</x:f>
+        <x:v>1160557.6923076927</x:v>
+      </x:c>
+      <x:c r="AB7" s="37" t="n">
+        <x:f>AA27</x:f>
+        <x:v>1160538.461538462</x:v>
+      </x:c>
+      <x:c r="AC7" s="37" t="n">
+        <x:f>AB27</x:f>
+        <x:v>1160519.2307692312</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1"/>
       <x:c r="C8" s="1" t="str">
-        <x:v>Open invoice collections</x:v>
+        <x:v>Opening invoice receipts</x:v>
       </x:c>
       <x:c r="D8" s="28" t="n">
         <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,D$5)</x:f>
@@ -3329,6 +3694,58 @@
       <x:c r="P8" s="28" t="n">
         <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,P$5)</x:f>
         <x:v>91000</x:v>
+      </x:c>
+      <x:c r="Q8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,Q$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,R$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,S$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,T$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,U$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,V$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,W$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,X$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,Y$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,Z$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,AA$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,AB$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC8" s="38" t="n">
+        <x:f>SUMIFS('Invoices'!$F$7:$F$32,'Invoices'!$H$7:$H$32,AC$5)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
@@ -3389,855 +3806,2500 @@
         <x:f>'Assumptions'!$G$11</x:f>
         <x:v>20000</x:v>
       </x:c>
+      <x:c r="Q9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="R9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="S9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="T9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="U9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="V9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="W9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="X9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="Y9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="Z9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="AA9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="AB9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="AC9" s="38" t="n">
+        <x:f>'Assumptions'!$G$11</x:f>
+        <x:v>20000</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1" t="str">
-        <x:v>Total receipts</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="n">
-        <x:f>SUM(D8:D9)</x:f>
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="n">
-        <x:f>SUM(E8:E9)</x:f>
-        <x:v>123000</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="n">
-        <x:f>SUM(F8:F9)</x:f>
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="n">
-        <x:f>SUM(G8:G9)</x:f>
-        <x:v>123000</x:v>
-      </x:c>
-      <x:c r="H10" s="29" t="n">
-        <x:f>SUM(H8:H9)</x:f>
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="I10" s="29" t="n">
-        <x:f>SUM(I8:I9)</x:f>
-        <x:v>123000</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:f>SUM(J8:J9)</x:f>
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="K10" s="29" t="n">
-        <x:f>SUM(K8:K9)</x:f>
-        <x:v>123000</x:v>
-      </x:c>
-      <x:c r="L10" s="29" t="n">
-        <x:f>SUM(L8:L9)</x:f>
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="n">
-        <x:f>SUM(M8:M9)</x:f>
-        <x:v>123000</x:v>
-      </x:c>
-      <x:c r="N10" s="29" t="n">
-        <x:f>SUM(N8:N9)</x:f>
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="O10" s="29" t="n">
-        <x:f>SUM(O8:O9)</x:f>
-        <x:v>123000</x:v>
-      </x:c>
-      <x:c r="P10" s="29" t="n">
-        <x:f>SUM(P8:P9)</x:f>
-        <x:v>111000</x:v>
+        <x:v>New invoice receipts</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,D$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,E$5)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,F$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="G10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,G$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="H10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,H$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="I10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,I$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="J10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,J$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="K10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,K$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="L10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,L$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="M10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,M$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="N10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,N$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="O10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,O$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="P10" s="28" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,P$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="Q10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,Q$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="R10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,R$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="S10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,S$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="T10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,T$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="U10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,U$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="V10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,V$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="W10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,W$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="X10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,X$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="Y10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,Y$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="Z10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,Z$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="AA10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,AA$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="AB10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,AB$5)</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="AC10" s="38" t="n">
+        <x:f>SUMIFS('New Invoices'!$E$7:$E$32,'New Invoices'!$F$7:$F$32,AC$5)</x:f>
+        <x:v>92000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1" t="str">
-        <x:v>Payroll</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="H11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="K11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="L11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="N11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="O11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="P11" s="28" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>45000</x:v>
+        <x:v>Total receipts</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="n">
+        <x:f>SUM(D8:D10)</x:f>
+        <x:v>111000</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="n">
+        <x:f>SUM(E8:E10)</x:f>
+        <x:v>123000</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="n">
+        <x:f>SUM(F8:F10)</x:f>
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="n">
+        <x:f>SUM(G8:G10)</x:f>
+        <x:v>215000</x:v>
+      </x:c>
+      <x:c r="H11" s="29" t="n">
+        <x:f>SUM(H8:H10)</x:f>
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="I11" s="29" t="n">
+        <x:f>SUM(I8:I10)</x:f>
+        <x:v>215000</x:v>
+      </x:c>
+      <x:c r="J11" s="29" t="n">
+        <x:f>SUM(J8:J10)</x:f>
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="K11" s="29" t="n">
+        <x:f>SUM(K8:K10)</x:f>
+        <x:v>215000</x:v>
+      </x:c>
+      <x:c r="L11" s="29" t="n">
+        <x:f>SUM(L8:L10)</x:f>
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="n">
+        <x:f>SUM(M8:M10)</x:f>
+        <x:v>215000</x:v>
+      </x:c>
+      <x:c r="N11" s="29" t="n">
+        <x:f>SUM(N8:N10)</x:f>
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="O11" s="29" t="n">
+        <x:f>SUM(O8:O10)</x:f>
+        <x:v>215000</x:v>
+      </x:c>
+      <x:c r="P11" s="29" t="n">
+        <x:f>SUM(P8:P10)</x:f>
+        <x:v>203000</x:v>
+      </x:c>
+      <x:c r="Q11" s="37" t="n">
+        <x:f>SUM(Q8:Q10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="R11" s="37" t="n">
+        <x:f>SUM(R8:R10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="S11" s="37" t="n">
+        <x:f>SUM(S8:S10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="T11" s="37" t="n">
+        <x:f>SUM(T8:T10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="U11" s="37" t="n">
+        <x:f>SUM(U8:U10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="V11" s="37" t="n">
+        <x:f>SUM(V8:V10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="W11" s="37" t="n">
+        <x:f>SUM(W8:W10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="X11" s="37" t="n">
+        <x:f>SUM(X8:X10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="Y11" s="37" t="n">
+        <x:f>SUM(Y8:Y10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="Z11" s="37" t="n">
+        <x:f>SUM(Z8:Z10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="AA11" s="37" t="n">
+        <x:f>SUM(AA8:AA10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="AB11" s="37" t="n">
+        <x:f>SUM(AB8:AB10)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="AC11" s="37" t="n">
+        <x:f>SUM(AC8:AC10)</x:f>
+        <x:v>112000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1"/>
       <x:c r="C12" s="1" t="str">
-        <x:v>Fuel</x:v>
+        <x:v>Payroll</x:v>
       </x:c>
       <x:c r="D12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="E12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="F12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="G12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="H12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="I12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="K12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="L12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="M12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="N12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="O12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="P12" s="28" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="Q12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="R12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="S12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="T12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="U12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="V12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="W12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="X12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="Y12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="Z12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="AA12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="AB12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="AC12" s="38" t="n">
+        <x:f>'Assumptions'!$G$12</x:f>
+        <x:v>45000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1"/>
       <x:c r="C13" s="1" t="str">
-        <x:v>Supplier payments</x:v>
+        <x:v>Fuel</x:v>
       </x:c>
       <x:c r="D13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="E13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="F13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="H13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="I13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="K13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="L13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="M13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="N13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="O13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="P13" s="28" t="n">
-        <x:f>'Assumptions'!$G$14</x:f>
-        <x:v>35000</x:v>
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="Q13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="R13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="S13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="T13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="U13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="V13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="W13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="X13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="Y13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="Z13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="AA13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="AB13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="AC13" s="38" t="n">
+        <x:f>'Assumptions'!$G$13</x:f>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1" t="str">
-        <x:v>Lease payments</x:v>
+        <x:v>Supplier payments</x:v>
       </x:c>
       <x:c r="D14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="E14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="F14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="G14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="H14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="I14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="J14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="K14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="L14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="M14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="N14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="O14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="P14" s="28" t="n">
-        <x:f>'Assumptions'!$G$15</x:f>
-        <x:v>12000</x:v>
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="Q14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="R14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="S14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="T14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="U14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="V14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="W14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="X14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="Y14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="Z14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="AA14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="AB14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="AC14" s="38" t="n">
+        <x:f>'Assumptions'!$G$14</x:f>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1" t="str">
-        <x:v>Capex</x:v>
+        <x:v>Lease payments</x:v>
       </x:c>
       <x:c r="D15" s="28" t="n">
-        <x:f>IF(D$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="E15" s="28" t="n">
-        <x:f>IF(E$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="F15" s="28" t="n">
-        <x:f>IF(F$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G15" s="28" t="n">
-        <x:f>IF(G$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="H15" s="28" t="n">
-        <x:f>IF(H$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="I15" s="28" t="n">
-        <x:f>IF(I$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>90000</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="J15" s="28" t="n">
-        <x:f>IF(J$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="K15" s="28" t="n">
-        <x:f>IF(K$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="L15" s="28" t="n">
-        <x:f>IF(L$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="M15" s="28" t="n">
-        <x:f>IF(M$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="N15" s="28" t="n">
-        <x:f>IF(N$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="O15" s="28" t="n">
-        <x:f>IF(O$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="P15" s="28" t="n">
-        <x:f>IF(P$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
-        <x:v>0</x:v>
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="Q15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="R15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="S15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="T15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="U15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="V15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="W15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="X15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="Y15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="Z15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="AA15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="AB15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="AC15" s="38" t="n">
+        <x:f>'Assumptions'!$G$15</x:f>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1"/>
       <x:c r="C16" s="1" t="str">
-        <x:v>Total payments</x:v>
-      </x:c>
-      <x:c r="D16" s="29" t="n">
-        <x:f>SUM(D11:D15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="E16" s="29" t="n">
-        <x:f>SUM(E11:E15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="F16" s="29" t="n">
-        <x:f>SUM(F11:F15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="G16" s="29" t="n">
-        <x:f>SUM(G11:G15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="H16" s="29" t="n">
-        <x:f>SUM(H11:H15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="I16" s="29" t="n">
-        <x:f>SUM(I11:I15)</x:f>
-        <x:v>202000</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="n">
-        <x:f>SUM(J11:J15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="K16" s="29" t="n">
-        <x:f>SUM(K11:K15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="L16" s="29" t="n">
-        <x:f>SUM(L11:L15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="M16" s="29" t="n">
-        <x:f>SUM(M11:M15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="N16" s="29" t="n">
-        <x:f>SUM(N11:N15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="O16" s="29" t="n">
-        <x:f>SUM(O11:O15)</x:f>
-        <x:v>112000</x:v>
-      </x:c>
-      <x:c r="P16" s="29" t="n">
-        <x:f>SUM(P11:P15)</x:f>
-        <x:v>112000</x:v>
+        <x:v>Capex</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="n">
+        <x:f>IF(D$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="28" t="n">
+        <x:f>IF(E$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="28" t="n">
+        <x:f>IF(F$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="n">
+        <x:f>IF(G$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="28" t="n">
+        <x:f>IF(H$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="28" t="n">
+        <x:f>IF(I$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>90000</x:v>
+      </x:c>
+      <x:c r="J16" s="28" t="n">
+        <x:f>IF(J$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="28" t="n">
+        <x:f>IF(K$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="28" t="n">
+        <x:f>IF(L$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="28" t="n">
+        <x:f>IF(M$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="28" t="n">
+        <x:f>IF(N$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="28" t="n">
+        <x:f>IF(O$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="28" t="n">
+        <x:f>IF(P$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="38" t="n">
+        <x:f>IF(Q$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R16" s="38" t="n">
+        <x:f>IF(R$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S16" s="38" t="n">
+        <x:f>IF(S$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T16" s="38" t="n">
+        <x:f>IF(T$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16" s="38" t="n">
+        <x:f>IF(U$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V16" s="38" t="n">
+        <x:f>IF(V$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W16" s="38" t="n">
+        <x:f>IF(W$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X16" s="38" t="n">
+        <x:f>IF(X$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y16" s="38" t="n">
+        <x:f>IF(Y$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z16" s="38" t="n">
+        <x:f>IF(Z$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA16" s="38" t="n">
+        <x:f>IF(AA$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB16" s="38" t="n">
+        <x:f>IF(AB$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC16" s="38" t="n">
+        <x:f>IF(AC$5='Assumptions'!$D$18,'Assumptions'!$G$16,0)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1"/>
       <x:c r="C17" s="1" t="str">
-        <x:v>Net cash flow</x:v>
+        <x:v>Total operating payments</x:v>
       </x:c>
       <x:c r="D17" s="29" t="n">
-        <x:f>D10-D16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(D12:D16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="E17" s="29" t="n">
-        <x:f>E10-E16</x:f>
-        <x:v>11000</x:v>
+        <x:f>SUM(E12:E16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="F17" s="29" t="n">
-        <x:f>F10-F16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(F12:F16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="G17" s="29" t="n">
-        <x:f>G10-G16</x:f>
-        <x:v>11000</x:v>
+        <x:f>SUM(G12:G16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="H17" s="29" t="n">
-        <x:f>H10-H16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(H12:H16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="I17" s="29" t="n">
-        <x:f>I10-I16</x:f>
-        <x:v>-79000</x:v>
+        <x:f>SUM(I12:I16)</x:f>
+        <x:v>202000</x:v>
       </x:c>
       <x:c r="J17" s="29" t="n">
-        <x:f>J10-J16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(J12:J16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="K17" s="29" t="n">
-        <x:f>K10-K16</x:f>
-        <x:v>11000</x:v>
+        <x:f>SUM(K12:K16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="L17" s="29" t="n">
-        <x:f>L10-L16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(L12:L16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="M17" s="29" t="n">
-        <x:f>M10-M16</x:f>
-        <x:v>11000</x:v>
+        <x:f>SUM(M12:M16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="N17" s="29" t="n">
-        <x:f>N10-N16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(N12:N16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="O17" s="29" t="n">
-        <x:f>O10-O16</x:f>
-        <x:v>11000</x:v>
+        <x:f>SUM(O12:O16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
       <x:c r="P17" s="29" t="n">
-        <x:f>P10-P16</x:f>
-        <x:v>-1000</x:v>
+        <x:f>SUM(P12:P16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="Q17" s="37" t="n">
+        <x:f>SUM(Q12:Q16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="R17" s="37" t="n">
+        <x:f>SUM(R12:R16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="S17" s="37" t="n">
+        <x:f>SUM(S12:S16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="T17" s="37" t="n">
+        <x:f>SUM(T12:T16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="U17" s="37" t="n">
+        <x:f>SUM(U12:U16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="V17" s="37" t="n">
+        <x:f>SUM(V12:V16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="W17" s="37" t="n">
+        <x:f>SUM(W12:W16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="X17" s="37" t="n">
+        <x:f>SUM(X12:X16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="Y17" s="37" t="n">
+        <x:f>SUM(Y12:Y16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="Z17" s="37" t="n">
+        <x:f>SUM(Z12:Z16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="AA17" s="37" t="n">
+        <x:f>SUM(AA12:AA16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="AB17" s="37" t="n">
+        <x:f>SUM(AB12:AB16)</x:f>
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="AC17" s="37" t="n">
+        <x:f>SUM(AC12:AC16)</x:f>
+        <x:v>112000</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1"/>
       <x:c r="C18" s="1" t="str">
-        <x:v>Ending cash before financing</x:v>
+        <x:v>Operating net cash flow</x:v>
       </x:c>
       <x:c r="D18" s="29" t="n">
-        <x:f>SUM(D7,D17)</x:f>
-        <x:v>179000</x:v>
+        <x:f>D11-D17</x:f>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="E18" s="29" t="n">
-        <x:f>SUM(E7,E17)</x:f>
-        <x:v>190000</x:v>
+        <x:f>E11-E17</x:f>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="F18" s="29" t="n">
-        <x:f>SUM(F7,F17)</x:f>
-        <x:v>189000</x:v>
+        <x:f>F11-F17</x:f>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="G18" s="29" t="n">
-        <x:f>SUM(G7,G17)</x:f>
-        <x:v>200000</x:v>
+        <x:f>G11-G17</x:f>
+        <x:v>103000</x:v>
       </x:c>
       <x:c r="H18" s="29" t="n">
-        <x:f>SUM(H7,H17)</x:f>
-        <x:v>199000</x:v>
+        <x:f>H11-H17</x:f>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="I18" s="29" t="n">
-        <x:f>SUM(I7,I17)</x:f>
-        <x:v>120000</x:v>
+        <x:f>I11-I17</x:f>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J18" s="29" t="n">
-        <x:f>SUM(J7,J17)</x:f>
-        <x:v>119000</x:v>
+        <x:f>J11-J17</x:f>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="K18" s="29" t="n">
-        <x:f>SUM(K7,K17)</x:f>
-        <x:v>130000</x:v>
+        <x:f>K11-K17</x:f>
+        <x:v>103000</x:v>
       </x:c>
       <x:c r="L18" s="29" t="n">
-        <x:f>SUM(L7,L17)</x:f>
-        <x:v>129000</x:v>
+        <x:f>L11-L17</x:f>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="M18" s="29" t="n">
-        <x:f>SUM(M7,M17)</x:f>
-        <x:v>140000</x:v>
+        <x:f>M11-M17</x:f>
+        <x:v>103000</x:v>
       </x:c>
       <x:c r="N18" s="29" t="n">
-        <x:f>SUM(N7,N17)</x:f>
-        <x:v>139000</x:v>
+        <x:f>N11-N17</x:f>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="O18" s="29" t="n">
-        <x:f>SUM(O7,O17)</x:f>
-        <x:v>150000</x:v>
+        <x:f>O11-O17</x:f>
+        <x:v>103000</x:v>
       </x:c>
       <x:c r="P18" s="29" t="n">
-        <x:f>SUM(P7,P17)</x:f>
-        <x:v>149000</x:v>
+        <x:f>P11-P17</x:f>
+        <x:v>91000</x:v>
+      </x:c>
+      <x:c r="Q18" s="37" t="n">
+        <x:f>Q11-Q17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="37" t="n">
+        <x:f>R11-R17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="37" t="n">
+        <x:f>S11-S17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T18" s="37" t="n">
+        <x:f>T11-T17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18" s="37" t="n">
+        <x:f>U11-U17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V18" s="37" t="n">
+        <x:f>V11-V17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W18" s="37" t="n">
+        <x:f>W11-W17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" s="37" t="n">
+        <x:f>X11-X17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y18" s="37" t="n">
+        <x:f>Y11-Y17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z18" s="37" t="n">
+        <x:f>Z11-Z17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA18" s="37" t="n">
+        <x:f>AA11-AA17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB18" s="37" t="n">
+        <x:f>AB11-AB17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC18" s="37" t="n">
+        <x:f>AC11-AC17</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1"/>
       <x:c r="C19" s="1" t="str">
-        <x:v>Minimum cash</x:v>
+        <x:v>Opening facility debt</x:v>
       </x:c>
       <x:c r="D19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="E19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="F19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="G19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="H19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="I19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="J19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="K19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="L19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="M19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="N19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="O19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="P19" s="28" t="n">
-        <x:f>'Assumptions'!$G$10</x:f>
-        <x:v>100000</x:v>
+        <x:f>'Assumptions'!I38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="29" t="n">
+        <x:f>D26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="29" t="n">
+        <x:f>E26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="n">
+        <x:f>F26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="29" t="n">
+        <x:f>G26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="29" t="n">
+        <x:f>H26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="29" t="n">
+        <x:f>I26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="29" t="n">
+        <x:f>J26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="29" t="n">
+        <x:f>K26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="29" t="n">
+        <x:f>L26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="29" t="n">
+        <x:f>M26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="29" t="n">
+        <x:f>N26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="29" t="n">
+        <x:f>O26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="37" t="n">
+        <x:f>P26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="37" t="n">
+        <x:f>Q26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" s="37" t="n">
+        <x:f>R26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T19" s="37" t="n">
+        <x:f>S26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19" s="37" t="n">
+        <x:f>T26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V19" s="37" t="n">
+        <x:f>U26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W19" s="37" t="n">
+        <x:f>V26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19" s="37" t="n">
+        <x:f>W26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y19" s="37" t="n">
+        <x:f>X26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" s="37" t="n">
+        <x:f>Y26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA19" s="37" t="n">
+        <x:f>Z26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB19" s="37" t="n">
+        <x:f>AA26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC19" s="37" t="n">
+        <x:f>AB26</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1"/>
       <x:c r="C20" s="1" t="str">
-        <x:v>Cumulative funding shortfall</x:v>
-      </x:c>
-      <x:c r="D20" s="29" t="n">
-        <x:f>MAX(0,D19-D18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="29" t="n">
-        <x:f>MAX(0,E19-E18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F20" s="29" t="n">
-        <x:f>MAX(0,F19-F18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="29" t="n">
-        <x:f>MAX(0,G19-G18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="29" t="n">
-        <x:f>MAX(0,H19-H18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I20" s="29" t="n">
-        <x:f>MAX(0,I19-I18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="29" t="n">
-        <x:f>MAX(0,J19-J18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K20" s="29" t="n">
-        <x:f>MAX(0,K19-K18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L20" s="29" t="n">
-        <x:f>MAX(0,L19-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M20" s="29" t="n">
-        <x:f>MAX(0,M19-M18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="29" t="n">
-        <x:f>MAX(0,N19-N18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O20" s="29" t="n">
-        <x:f>MAX(0,O19-O18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P20" s="29" t="n">
-        <x:f>MAX(0,P19-P18)</x:f>
+        <x:v>Interest on opening debt</x:v>
+      </x:c>
+      <x:c r="D20" s="28" t="n">
+        <x:f>D19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="28" t="n">
+        <x:f>E19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="28" t="n">
+        <x:f>F19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="n">
+        <x:f>G19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="28" t="n">
+        <x:f>H19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="28" t="n">
+        <x:f>I19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="28" t="n">
+        <x:f>J19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="28" t="n">
+        <x:f>K19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="28" t="n">
+        <x:f>L19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="28" t="n">
+        <x:f>M19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="28" t="n">
+        <x:f>N19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="28" t="n">
+        <x:f>O19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="28" t="n">
+        <x:f>P19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="38" t="n">
+        <x:f>Q19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R20" s="38" t="n">
+        <x:f>R19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S20" s="38" t="n">
+        <x:f>S19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T20" s="38" t="n">
+        <x:f>T19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20" s="38" t="n">
+        <x:f>U19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V20" s="38" t="n">
+        <x:f>V19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W20" s="38" t="n">
+        <x:f>W19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X20" s="38" t="n">
+        <x:f>X19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y20" s="38" t="n">
+        <x:f>Y19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z20" s="38" t="n">
+        <x:f>Z19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA20" s="38" t="n">
+        <x:f>AA19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB20" s="38" t="n">
+        <x:f>AB19*'Assumptions'!$I$36/52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC20" s="38" t="n">
+        <x:f>AC19*'Assumptions'!$I$36/52</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1"/>
-      <x:c r="C21" s="1"/>
-      <x:c r="D21" s="1"/>
-      <x:c r="E21" s="1"/>
-      <x:c r="F21" s="1"/>
-      <x:c r="G21" s="1"/>
-      <x:c r="H21" s="1"/>
-      <x:c r="I21" s="1"/>
-      <x:c r="J21" s="1"/>
-      <x:c r="K21" s="1"/>
-      <x:c r="L21" s="1"/>
-      <x:c r="M21" s="1"/>
-      <x:c r="N21" s="1"/>
-      <x:c r="O21" s="1"/>
-      <x:c r="P21" s="1"/>
+      <x:c r="C21" s="1" t="str">
+        <x:v>Undrawn commitment fee</x:v>
+      </x:c>
+      <x:c r="D21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-D19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="E21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-E19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="F21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-F19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-G19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="H21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-H19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="I21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-I19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="J21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-J19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="K21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-K19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="L21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-L19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="M21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-M19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="N21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-N19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="O21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-O19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="P21" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-P19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="Q21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-Q19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="R21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-R19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="S21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-S19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="T21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-T19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="U21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-U19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="V21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-V19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="W21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-W19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="X21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-X19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="Y21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-Y19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="Z21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-Z19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="AA21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-AA19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="AB21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-AB19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="AC21" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-AC19)*'Assumptions'!$I$37/52</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1"/>
-      <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1"/>
-      <x:c r="H22" s="1"/>
-      <x:c r="I22" s="1"/>
-      <x:c r="J22" s="1"/>
-      <x:c r="K22" s="1"/>
-      <x:c r="L22" s="1"/>
-      <x:c r="M22" s="1"/>
-      <x:c r="N22" s="1"/>
-      <x:c r="O22" s="1"/>
-      <x:c r="P22" s="1"/>
+      <x:c r="C22" s="1" t="str">
+        <x:v>Cash before draw / repayment</x:v>
+      </x:c>
+      <x:c r="D22" s="29" t="n">
+        <x:f>D7+D18-SUM(D20:D21)</x:f>
+        <x:v>178980.76923076922</x:v>
+      </x:c>
+      <x:c r="E22" s="29" t="n">
+        <x:f>E7+E18-SUM(E20:E21)</x:f>
+        <x:v>189961.53846153844</x:v>
+      </x:c>
+      <x:c r="F22" s="29" t="n">
+        <x:f>F7+F18-SUM(F20:F21)</x:f>
+        <x:v>280942.3076923077</x:v>
+      </x:c>
+      <x:c r="G22" s="29" t="n">
+        <x:f>G7+G18-SUM(G20:G21)</x:f>
+        <x:v>383923.07692307694</x:v>
+      </x:c>
+      <x:c r="H22" s="29" t="n">
+        <x:f>H7+H18-SUM(H20:H21)</x:f>
+        <x:v>474903.8461538462</x:v>
+      </x:c>
+      <x:c r="I22" s="29" t="n">
+        <x:f>I7+I18-SUM(I20:I21)</x:f>
+        <x:v>487884.61538461543</x:v>
+      </x:c>
+      <x:c r="J22" s="29" t="n">
+        <x:f>J7+J18-SUM(J20:J21)</x:f>
+        <x:v>578865.3846153847</x:v>
+      </x:c>
+      <x:c r="K22" s="29" t="n">
+        <x:f>K7+K18-SUM(K20:K21)</x:f>
+        <x:v>681846.153846154</x:v>
+      </x:c>
+      <x:c r="L22" s="29" t="n">
+        <x:f>L7+L18-SUM(L20:L21)</x:f>
+        <x:v>772826.9230769232</x:v>
+      </x:c>
+      <x:c r="M22" s="29" t="n">
+        <x:f>M7+M18-SUM(M20:M21)</x:f>
+        <x:v>875807.6923076925</x:v>
+      </x:c>
+      <x:c r="N22" s="29" t="n">
+        <x:f>N7+N18-SUM(N20:N21)</x:f>
+        <x:v>966788.4615384617</x:v>
+      </x:c>
+      <x:c r="O22" s="29" t="n">
+        <x:f>O7+O18-SUM(O20:O21)</x:f>
+        <x:v>1069769.230769231</x:v>
+      </x:c>
+      <x:c r="P22" s="29" t="n">
+        <x:f>P7+P18-SUM(P20:P21)</x:f>
+        <x:v>1160750.0000000002</x:v>
+      </x:c>
+      <x:c r="Q22" s="37" t="n">
+        <x:f>Q7+Q18-SUM(Q20:Q21)</x:f>
+        <x:v>1160730.7692307695</x:v>
+      </x:c>
+      <x:c r="R22" s="37" t="n">
+        <x:f>R7+R18-SUM(R20:R21)</x:f>
+        <x:v>1160711.5384615387</x:v>
+      </x:c>
+      <x:c r="S22" s="37" t="n">
+        <x:f>S7+S18-SUM(S20:S21)</x:f>
+        <x:v>1160692.307692308</x:v>
+      </x:c>
+      <x:c r="T22" s="37" t="n">
+        <x:f>T7+T18-SUM(T20:T21)</x:f>
+        <x:v>1160673.0769230772</x:v>
+      </x:c>
+      <x:c r="U22" s="37" t="n">
+        <x:f>U7+U18-SUM(U20:U21)</x:f>
+        <x:v>1160653.8461538465</x:v>
+      </x:c>
+      <x:c r="V22" s="37" t="n">
+        <x:f>V7+V18-SUM(V20:V21)</x:f>
+        <x:v>1160634.6153846157</x:v>
+      </x:c>
+      <x:c r="W22" s="37" t="n">
+        <x:f>W7+W18-SUM(W20:W21)</x:f>
+        <x:v>1160615.384615385</x:v>
+      </x:c>
+      <x:c r="X22" s="37" t="n">
+        <x:f>X7+X18-SUM(X20:X21)</x:f>
+        <x:v>1160596.1538461542</x:v>
+      </x:c>
+      <x:c r="Y22" s="37" t="n">
+        <x:f>Y7+Y18-SUM(Y20:Y21)</x:f>
+        <x:v>1160576.9230769235</x:v>
+      </x:c>
+      <x:c r="Z22" s="37" t="n">
+        <x:f>Z7+Z18-SUM(Z20:Z21)</x:f>
+        <x:v>1160557.6923076927</x:v>
+      </x:c>
+      <x:c r="AA22" s="37" t="n">
+        <x:f>AA7+AA18-SUM(AA20:AA21)</x:f>
+        <x:v>1160538.461538462</x:v>
+      </x:c>
+      <x:c r="AB22" s="37" t="n">
+        <x:f>AB7+AB18-SUM(AB20:AB21)</x:f>
+        <x:v>1160519.2307692312</x:v>
+      </x:c>
+      <x:c r="AC22" s="37" t="n">
+        <x:f>AC7+AC18-SUM(AC20:AC21)</x:f>
+        <x:v>1160500.0000000005</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1"/>
       <x:c r="C23" s="5" t="str">
-        <x:v>Funding shortfall is a requirement, not an assumed available credit line.</x:v>
-      </x:c>
-      <x:c r="D23" s="5"/>
-      <x:c r="E23" s="5"/>
-      <x:c r="F23" s="5"/>
-      <x:c r="G23" s="5"/>
-      <x:c r="H23" s="5"/>
-      <x:c r="I23" s="5"/>
-      <x:c r="J23" s="5"/>
-      <x:c r="K23" s="5"/>
-      <x:c r="L23" s="5"/>
-      <x:c r="M23" s="1"/>
-      <x:c r="N23" s="1"/>
-      <x:c r="O23" s="1"/>
-      <x:c r="P23" s="1"/>
+        <x:v>Available commitment</x:v>
+      </x:c>
+      <x:c r="D23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-D19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-E19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-F19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-G19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="H23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-H19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="I23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-I19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-J19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="K23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-K19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="L23" s="30" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-L19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="M23" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-M19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="N23" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-N19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="O23" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-O19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="P23" s="28" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-P19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="Q23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-Q19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="R23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-R19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="S23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-S19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="T23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-T19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="U23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-U19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="V23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-V19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="W23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-W19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="X23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-X19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="Y23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-Y19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="Z23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-Z19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="AA23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-AA19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="AB23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-AB19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="AC23" s="38" t="n">
+        <x:f>MAX(0,'Assumptions'!$I$35-AC19)</x:f>
+        <x:v>200000</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1"/>
-      <x:c r="C24" s="5"/>
-      <x:c r="D24" s="5"/>
-      <x:c r="E24" s="5"/>
-      <x:c r="F24" s="5"/>
-      <x:c r="G24" s="5"/>
-      <x:c r="H24" s="5"/>
-      <x:c r="I24" s="5"/>
-      <x:c r="J24" s="5"/>
-      <x:c r="K24" s="5"/>
-      <x:c r="L24" s="5"/>
-      <x:c r="M24" s="1"/>
-      <x:c r="N24" s="1"/>
-      <x:c r="O24" s="1"/>
-      <x:c r="P24" s="1"/>
+      <x:c r="C24" s="5" t="str">
+        <x:v>Facility draw</x:v>
+      </x:c>
+      <x:c r="D24" s="30" t="n">
+        <x:f>MIN(D23,MAX(0,'Assumptions'!$G$10-D22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="n">
+        <x:f>MIN(E23,MAX(0,'Assumptions'!$G$10-E22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="30" t="n">
+        <x:f>MIN(F23,MAX(0,'Assumptions'!$G$10-F22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="n">
+        <x:f>MIN(G23,MAX(0,'Assumptions'!$G$10-G22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" s="30" t="n">
+        <x:f>MIN(H23,MAX(0,'Assumptions'!$G$10-H22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="30" t="n">
+        <x:f>MIN(I23,MAX(0,'Assumptions'!$G$10-I22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="30" t="n">
+        <x:f>MIN(J23,MAX(0,'Assumptions'!$G$10-J22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" s="30" t="n">
+        <x:f>MIN(K23,MAX(0,'Assumptions'!$G$10-K22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24" s="30" t="n">
+        <x:f>MIN(L23,MAX(0,'Assumptions'!$G$10-L22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" s="28" t="n">
+        <x:f>MIN(M23,MAX(0,'Assumptions'!$G$10-M22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N24" s="28" t="n">
+        <x:f>MIN(N23,MAX(0,'Assumptions'!$G$10-N22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O24" s="28" t="n">
+        <x:f>MIN(O23,MAX(0,'Assumptions'!$G$10-O22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P24" s="28" t="n">
+        <x:f>MIN(P23,MAX(0,'Assumptions'!$G$10-P22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="38" t="n">
+        <x:f>MIN(Q23,MAX(0,'Assumptions'!$G$10-Q22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R24" s="38" t="n">
+        <x:f>MIN(R23,MAX(0,'Assumptions'!$G$10-R22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S24" s="38" t="n">
+        <x:f>MIN(S23,MAX(0,'Assumptions'!$G$10-S22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T24" s="38" t="n">
+        <x:f>MIN(T23,MAX(0,'Assumptions'!$G$10-T22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U24" s="38" t="n">
+        <x:f>MIN(U23,MAX(0,'Assumptions'!$G$10-U22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V24" s="38" t="n">
+        <x:f>MIN(V23,MAX(0,'Assumptions'!$G$10-V22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W24" s="38" t="n">
+        <x:f>MIN(W23,MAX(0,'Assumptions'!$G$10-W22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X24" s="38" t="n">
+        <x:f>MIN(X23,MAX(0,'Assumptions'!$G$10-X22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y24" s="38" t="n">
+        <x:f>MIN(Y23,MAX(0,'Assumptions'!$G$10-Y22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z24" s="38" t="n">
+        <x:f>MIN(Z23,MAX(0,'Assumptions'!$G$10-Z22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA24" s="38" t="n">
+        <x:f>MIN(AA23,MAX(0,'Assumptions'!$G$10-AA22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB24" s="38" t="n">
+        <x:f>MIN(AB23,MAX(0,'Assumptions'!$G$10-AB22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC24" s="38" t="n">
+        <x:f>MIN(AC23,MAX(0,'Assumptions'!$G$10-AC22))</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1"/>
-      <x:c r="C25" s="1"/>
-      <x:c r="D25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="1"/>
-      <x:c r="G25" s="1"/>
-      <x:c r="H25" s="1"/>
-      <x:c r="I25" s="1"/>
-      <x:c r="J25" s="1"/>
-      <x:c r="K25" s="1"/>
-      <x:c r="L25" s="1"/>
-      <x:c r="M25" s="1"/>
-      <x:c r="N25" s="1"/>
-      <x:c r="O25" s="1"/>
-      <x:c r="P25" s="1"/>
+      <x:c r="C25" s="1" t="str">
+        <x:v>Facility repayment</x:v>
+      </x:c>
+      <x:c r="D25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(D19,MAX(0,D22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(E19,MAX(0,E22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(F19,MAX(0,F22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(G19,MAX(0,G22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(H19,MAX(0,H22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(I19,MAX(0,I22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(J19,MAX(0,J22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(K19,MAX(0,K22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(L19,MAX(0,L22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(M19,MAX(0,M22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(N19,MAX(0,N22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(O19,MAX(0,O22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P25" s="28" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(P19,MAX(0,P22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(Q19,MAX(0,Q22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(R19,MAX(0,R22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(S19,MAX(0,S22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(T19,MAX(0,T22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(U19,MAX(0,U22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(V19,MAX(0,V22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(W19,MAX(0,W22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(X19,MAX(0,X22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(Y19,MAX(0,Y22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(Z19,MAX(0,Z22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(AA19,MAX(0,AA22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(AB19,MAX(0,AB22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC25" s="38" t="n">
+        <x:f>IF('Assumptions'!$I$42=1,MIN(AC19,MAX(0,AC22-'Assumptions'!$G$10)),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
-      <x:c r="I26" s="1"/>
-      <x:c r="J26" s="1"/>
-      <x:c r="K26" s="1"/>
-      <x:c r="L26" s="1"/>
-      <x:c r="M26" s="1"/>
-      <x:c r="N26" s="1"/>
-      <x:c r="O26" s="1"/>
-      <x:c r="P26" s="1"/>
+      <x:c r="C26" s="1" t="str">
+        <x:v>Closing facility debt</x:v>
+      </x:c>
+      <x:c r="D26" s="29" t="n">
+        <x:f>D19+D24-D25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="29" t="n">
+        <x:f>E19+E24-E25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="29" t="n">
+        <x:f>F19+F24-F25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="n">
+        <x:f>G19+G24-G25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="29" t="n">
+        <x:f>H19+H24-H25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="29" t="n">
+        <x:f>I19+I24-I25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="n">
+        <x:f>J19+J24-J25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="29" t="n">
+        <x:f>K19+K24-K25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="29" t="n">
+        <x:f>L19+L24-L25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="29" t="n">
+        <x:f>M19+M24-M25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="29" t="n">
+        <x:f>N19+N24-N25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="29" t="n">
+        <x:f>O19+O24-O25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P26" s="29" t="n">
+        <x:f>P19+P24-P25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q26" s="37" t="n">
+        <x:f>Q19+Q24-Q25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R26" s="37" t="n">
+        <x:f>R19+R24-R25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S26" s="37" t="n">
+        <x:f>S19+S24-S25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T26" s="37" t="n">
+        <x:f>T19+T24-T25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U26" s="37" t="n">
+        <x:f>U19+U24-U25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V26" s="37" t="n">
+        <x:f>V19+V24-V25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W26" s="37" t="n">
+        <x:f>W19+W24-W25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X26" s="37" t="n">
+        <x:f>X19+X24-X25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y26" s="37" t="n">
+        <x:f>Y19+Y24-Y25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z26" s="37" t="n">
+        <x:f>Z19+Z24-Z25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA26" s="37" t="n">
+        <x:f>AA19+AA24-AA25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB26" s="37" t="n">
+        <x:f>AB19+AB24-AB25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC26" s="37" t="n">
+        <x:f>AC19+AC24-AC25</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="1"/>
-      <x:c r="C27" s="1"/>
-      <x:c r="D27" s="1"/>
-      <x:c r="E27" s="1"/>
-      <x:c r="F27" s="1"/>
-      <x:c r="G27" s="1"/>
-      <x:c r="H27" s="1"/>
-      <x:c r="I27" s="1"/>
-      <x:c r="J27" s="1"/>
-      <x:c r="K27" s="1"/>
-      <x:c r="L27" s="1"/>
-      <x:c r="M27" s="1"/>
-      <x:c r="N27" s="1"/>
-      <x:c r="O27" s="1"/>
-      <x:c r="P27" s="1"/>
+      <x:c r="C27" s="1" t="str">
+        <x:v>Closing funded cash</x:v>
+      </x:c>
+      <x:c r="D27" s="29" t="n">
+        <x:f>D22+D24-D25</x:f>
+        <x:v>178980.76923076922</x:v>
+      </x:c>
+      <x:c r="E27" s="29" t="n">
+        <x:f>E22+E24-E25</x:f>
+        <x:v>189961.53846153844</x:v>
+      </x:c>
+      <x:c r="F27" s="29" t="n">
+        <x:f>F22+F24-F25</x:f>
+        <x:v>280942.3076923077</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="n">
+        <x:f>G22+G24-G25</x:f>
+        <x:v>383923.07692307694</x:v>
+      </x:c>
+      <x:c r="H27" s="29" t="n">
+        <x:f>H22+H24-H25</x:f>
+        <x:v>474903.8461538462</x:v>
+      </x:c>
+      <x:c r="I27" s="29" t="n">
+        <x:f>I22+I24-I25</x:f>
+        <x:v>487884.61538461543</x:v>
+      </x:c>
+      <x:c r="J27" s="29" t="n">
+        <x:f>J22+J24-J25</x:f>
+        <x:v>578865.3846153847</x:v>
+      </x:c>
+      <x:c r="K27" s="29" t="n">
+        <x:f>K22+K24-K25</x:f>
+        <x:v>681846.153846154</x:v>
+      </x:c>
+      <x:c r="L27" s="29" t="n">
+        <x:f>L22+L24-L25</x:f>
+        <x:v>772826.9230769232</x:v>
+      </x:c>
+      <x:c r="M27" s="29" t="n">
+        <x:f>M22+M24-M25</x:f>
+        <x:v>875807.6923076925</x:v>
+      </x:c>
+      <x:c r="N27" s="29" t="n">
+        <x:f>N22+N24-N25</x:f>
+        <x:v>966788.4615384617</x:v>
+      </x:c>
+      <x:c r="O27" s="29" t="n">
+        <x:f>O22+O24-O25</x:f>
+        <x:v>1069769.230769231</x:v>
+      </x:c>
+      <x:c r="P27" s="29" t="n">
+        <x:f>P22+P24-P25</x:f>
+        <x:v>1160750.0000000002</x:v>
+      </x:c>
+      <x:c r="Q27" s="37" t="n">
+        <x:f>Q22+Q24-Q25</x:f>
+        <x:v>1160730.7692307695</x:v>
+      </x:c>
+      <x:c r="R27" s="37" t="n">
+        <x:f>R22+R24-R25</x:f>
+        <x:v>1160711.5384615387</x:v>
+      </x:c>
+      <x:c r="S27" s="37" t="n">
+        <x:f>S22+S24-S25</x:f>
+        <x:v>1160692.307692308</x:v>
+      </x:c>
+      <x:c r="T27" s="37" t="n">
+        <x:f>T22+T24-T25</x:f>
+        <x:v>1160673.0769230772</x:v>
+      </x:c>
+      <x:c r="U27" s="37" t="n">
+        <x:f>U22+U24-U25</x:f>
+        <x:v>1160653.8461538465</x:v>
+      </x:c>
+      <x:c r="V27" s="37" t="n">
+        <x:f>V22+V24-V25</x:f>
+        <x:v>1160634.6153846157</x:v>
+      </x:c>
+      <x:c r="W27" s="37" t="n">
+        <x:f>W22+W24-W25</x:f>
+        <x:v>1160615.384615385</x:v>
+      </x:c>
+      <x:c r="X27" s="37" t="n">
+        <x:f>X22+X24-X25</x:f>
+        <x:v>1160596.1538461542</x:v>
+      </x:c>
+      <x:c r="Y27" s="37" t="n">
+        <x:f>Y22+Y24-Y25</x:f>
+        <x:v>1160576.9230769235</x:v>
+      </x:c>
+      <x:c r="Z27" s="37" t="n">
+        <x:f>Z22+Z24-Z25</x:f>
+        <x:v>1160557.6923076927</x:v>
+      </x:c>
+      <x:c r="AA27" s="37" t="n">
+        <x:f>AA22+AA24-AA25</x:f>
+        <x:v>1160538.461538462</x:v>
+      </x:c>
+      <x:c r="AB27" s="37" t="n">
+        <x:f>AB22+AB24-AB25</x:f>
+        <x:v>1160519.2307692312</x:v>
+      </x:c>
+      <x:c r="AC27" s="37" t="n">
+        <x:f>AC22+AC24-AC25</x:f>
+        <x:v>1160500.0000000005</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1"/>
-      <x:c r="C28" s="1"/>
-      <x:c r="D28" s="1"/>
-      <x:c r="E28" s="1"/>
-      <x:c r="F28" s="1"/>
-      <x:c r="G28" s="1"/>
-      <x:c r="H28" s="1"/>
-      <x:c r="I28" s="1"/>
-      <x:c r="J28" s="1"/>
-      <x:c r="K28" s="1"/>
-      <x:c r="L28" s="1"/>
-      <x:c r="M28" s="1"/>
-      <x:c r="N28" s="1"/>
-      <x:c r="O28" s="1"/>
-      <x:c r="P28" s="1"/>
+      <x:c r="C28" s="1" t="str">
+        <x:v>Minimum cash floor</x:v>
+      </x:c>
+      <x:c r="D28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="E28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="F28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="H28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="I28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="J28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="K28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="L28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="M28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="N28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="O28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="P28" s="28" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="Q28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="R28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="S28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="T28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="U28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="V28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="W28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="X28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="Y28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="Z28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="AA28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="AB28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="AC28" s="38" t="n">
+        <x:f>'Assumptions'!$G$10</x:f>
+        <x:v>100000</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1"/>
-      <x:c r="C29" s="1"/>
-      <x:c r="D29" s="1"/>
-      <x:c r="E29" s="1"/>
-      <x:c r="F29" s="1"/>
-      <x:c r="G29" s="1"/>
-      <x:c r="H29" s="1"/>
-      <x:c r="I29" s="1"/>
-      <x:c r="J29" s="1"/>
-      <x:c r="K29" s="1"/>
-      <x:c r="L29" s="1"/>
-      <x:c r="M29" s="1"/>
-      <x:c r="N29" s="1"/>
-      <x:c r="O29" s="1"/>
-      <x:c r="P29" s="1"/>
+      <x:c r="C29" s="1" t="str">
+        <x:v>Residual funding shortfall</x:v>
+      </x:c>
+      <x:c r="D29" s="29" t="n">
+        <x:f>MAX(0,D28-D27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="29" t="n">
+        <x:f>MAX(0,E28-E27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="29" t="n">
+        <x:f>MAX(0,F28-F27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="n">
+        <x:f>MAX(0,G28-G27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="29" t="n">
+        <x:f>MAX(0,H28-H27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="29" t="n">
+        <x:f>MAX(0,I28-I27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="29" t="n">
+        <x:f>MAX(0,J28-J27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="29" t="n">
+        <x:f>MAX(0,K28-K27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="29" t="n">
+        <x:f>MAX(0,L28-L27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="29" t="n">
+        <x:f>MAX(0,M28-M27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="29" t="n">
+        <x:f>MAX(0,N28-N27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="29" t="n">
+        <x:f>MAX(0,O28-O27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P29" s="29" t="n">
+        <x:f>MAX(0,P28-P27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q29" s="37" t="n">
+        <x:f>MAX(0,Q28-Q27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R29" s="37" t="n">
+        <x:f>MAX(0,R28-R27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S29" s="37" t="n">
+        <x:f>MAX(0,S28-S27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T29" s="37" t="n">
+        <x:f>MAX(0,T28-T27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U29" s="37" t="n">
+        <x:f>MAX(0,U28-U27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V29" s="37" t="n">
+        <x:f>MAX(0,V28-V27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W29" s="37" t="n">
+        <x:f>MAX(0,W28-W27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X29" s="37" t="n">
+        <x:f>MAX(0,X28-X27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y29" s="37" t="n">
+        <x:f>MAX(0,Y28-Y27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z29" s="37" t="n">
+        <x:f>MAX(0,Z28-Z27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA29" s="37" t="n">
+        <x:f>MAX(0,AA28-AA27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB29" s="37" t="n">
+        <x:f>MAX(0,AB28-AB27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC29" s="37" t="n">
+        <x:f>MAX(0,AC28-AC27)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1"/>
-      <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="1"/>
-      <x:c r="G30" s="1"/>
-      <x:c r="H30" s="1"/>
-      <x:c r="I30" s="1"/>
-      <x:c r="J30" s="1"/>
-      <x:c r="K30" s="1"/>
-      <x:c r="L30" s="1"/>
-      <x:c r="M30" s="1"/>
-      <x:c r="N30" s="1"/>
-      <x:c r="O30" s="1"/>
-      <x:c r="P30" s="1"/>
+      <x:c r="C30" s="1" t="str">
+        <x:v>Unfunded cash without facility</x:v>
+      </x:c>
+      <x:c r="D30" s="28" t="n">
+        <x:f>'Assumptions'!G9+D18</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="E30" s="29" t="n">
+        <x:f>D30+E18</x:f>
+        <x:v>190000</x:v>
+      </x:c>
+      <x:c r="F30" s="29" t="n">
+        <x:f>E30+F18</x:f>
+        <x:v>281000</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="n">
+        <x:f>F30+G18</x:f>
+        <x:v>384000</x:v>
+      </x:c>
+      <x:c r="H30" s="29" t="n">
+        <x:f>G30+H18</x:f>
+        <x:v>475000</x:v>
+      </x:c>
+      <x:c r="I30" s="29" t="n">
+        <x:f>H30+I18</x:f>
+        <x:v>488000</x:v>
+      </x:c>
+      <x:c r="J30" s="29" t="n">
+        <x:f>I30+J18</x:f>
+        <x:v>579000</x:v>
+      </x:c>
+      <x:c r="K30" s="29" t="n">
+        <x:f>J30+K18</x:f>
+        <x:v>682000</x:v>
+      </x:c>
+      <x:c r="L30" s="29" t="n">
+        <x:f>K30+L18</x:f>
+        <x:v>773000</x:v>
+      </x:c>
+      <x:c r="M30" s="29" t="n">
+        <x:f>L30+M18</x:f>
+        <x:v>876000</x:v>
+      </x:c>
+      <x:c r="N30" s="29" t="n">
+        <x:f>M30+N18</x:f>
+        <x:v>967000</x:v>
+      </x:c>
+      <x:c r="O30" s="29" t="n">
+        <x:f>N30+O18</x:f>
+        <x:v>1070000</x:v>
+      </x:c>
+      <x:c r="P30" s="29" t="n">
+        <x:f>O30+P18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="Q30" s="37" t="n">
+        <x:f>P30+Q18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="R30" s="37" t="n">
+        <x:f>Q30+R18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="S30" s="37" t="n">
+        <x:f>R30+S18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="T30" s="37" t="n">
+        <x:f>S30+T18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="U30" s="37" t="n">
+        <x:f>T30+U18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="V30" s="37" t="n">
+        <x:f>U30+V18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="W30" s="37" t="n">
+        <x:f>V30+W18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="X30" s="37" t="n">
+        <x:f>W30+X18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="Y30" s="37" t="n">
+        <x:f>X30+Y18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="Z30" s="37" t="n">
+        <x:f>Y30+Z18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="AA30" s="37" t="n">
+        <x:f>Z30+AA18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="AB30" s="37" t="n">
+        <x:f>AA30+AB18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
+      <x:c r="AC30" s="37" t="n">
+        <x:f>AB30+AC18</x:f>
+        <x:v>1161000</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="1"/>
-      <x:c r="G31" s="1"/>
-      <x:c r="H31" s="1"/>
-      <x:c r="I31" s="1"/>
-      <x:c r="J31" s="1"/>
-      <x:c r="K31" s="1"/>
-      <x:c r="L31" s="1"/>
-      <x:c r="M31" s="1"/>
-      <x:c r="N31" s="1"/>
-      <x:c r="O31" s="1"/>
-      <x:c r="P31" s="1"/>
+      <x:c r="C31" s="1" t="str">
+        <x:v>Cumulative net funding costs</x:v>
+      </x:c>
+      <x:c r="D31" s="29" t="n">
+        <x:f>SUM(D20:D21)</x:f>
+        <x:v>19.23076923076923</x:v>
+      </x:c>
+      <x:c r="E31" s="29" t="n">
+        <x:f>D31+SUM(E20:E21)</x:f>
+        <x:v>38.46153846153846</x:v>
+      </x:c>
+      <x:c r="F31" s="29" t="n">
+        <x:f>E31+SUM(F20:F21)</x:f>
+        <x:v>57.69230769230769</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="n">
+        <x:f>F31+SUM(G20:G21)</x:f>
+        <x:v>76.92307692307692</x:v>
+      </x:c>
+      <x:c r="H31" s="29" t="n">
+        <x:f>G31+SUM(H20:H21)</x:f>
+        <x:v>96.15384615384615</x:v>
+      </x:c>
+      <x:c r="I31" s="29" t="n">
+        <x:f>H31+SUM(I20:I21)</x:f>
+        <x:v>115.38461538461537</x:v>
+      </x:c>
+      <x:c r="J31" s="29" t="n">
+        <x:f>I31+SUM(J20:J21)</x:f>
+        <x:v>134.6153846153846</x:v>
+      </x:c>
+      <x:c r="K31" s="29" t="n">
+        <x:f>J31+SUM(K20:K21)</x:f>
+        <x:v>153.84615384615384</x:v>
+      </x:c>
+      <x:c r="L31" s="29" t="n">
+        <x:f>K31+SUM(L20:L21)</x:f>
+        <x:v>173.07692307692307</x:v>
+      </x:c>
+      <x:c r="M31" s="29" t="n">
+        <x:f>L31+SUM(M20:M21)</x:f>
+        <x:v>192.3076923076923</x:v>
+      </x:c>
+      <x:c r="N31" s="29" t="n">
+        <x:f>M31+SUM(N20:N21)</x:f>
+        <x:v>211.53846153846152</x:v>
+      </x:c>
+      <x:c r="O31" s="29" t="n">
+        <x:f>N31+SUM(O20:O21)</x:f>
+        <x:v>230.76923076923075</x:v>
+      </x:c>
+      <x:c r="P31" s="29" t="n">
+        <x:f>O31+SUM(P20:P21)</x:f>
+        <x:v>249.99999999999997</x:v>
+      </x:c>
+      <x:c r="Q31" s="37" t="n">
+        <x:f>P31+SUM(Q20:Q21)</x:f>
+        <x:v>269.2307692307692</x:v>
+      </x:c>
+      <x:c r="R31" s="37" t="n">
+        <x:f>Q31+SUM(R20:R21)</x:f>
+        <x:v>288.46153846153845</x:v>
+      </x:c>
+      <x:c r="S31" s="37" t="n">
+        <x:f>R31+SUM(S20:S21)</x:f>
+        <x:v>307.6923076923077</x:v>
+      </x:c>
+      <x:c r="T31" s="37" t="n">
+        <x:f>S31+SUM(T20:T21)</x:f>
+        <x:v>326.9230769230769</x:v>
+      </x:c>
+      <x:c r="U31" s="37" t="n">
+        <x:f>T31+SUM(U20:U21)</x:f>
+        <x:v>346.15384615384613</x:v>
+      </x:c>
+      <x:c r="V31" s="37" t="n">
+        <x:f>U31+SUM(V20:V21)</x:f>
+        <x:v>365.38461538461536</x:v>
+      </x:c>
+      <x:c r="W31" s="37" t="n">
+        <x:f>V31+SUM(W20:W21)</x:f>
+        <x:v>384.6153846153846</x:v>
+      </x:c>
+      <x:c r="X31" s="37" t="n">
+        <x:f>W31+SUM(X20:X21)</x:f>
+        <x:v>403.8461538461538</x:v>
+      </x:c>
+      <x:c r="Y31" s="37" t="n">
+        <x:f>X31+SUM(Y20:Y21)</x:f>
+        <x:v>423.07692307692304</x:v>
+      </x:c>
+      <x:c r="Z31" s="37" t="n">
+        <x:f>Y31+SUM(Z20:Z21)</x:f>
+        <x:v>442.30769230769226</x:v>
+      </x:c>
+      <x:c r="AA31" s="37" t="n">
+        <x:f>Z31+SUM(AA20:AA21)</x:f>
+        <x:v>461.5384615384615</x:v>
+      </x:c>
+      <x:c r="AB31" s="37" t="n">
+        <x:f>AA31+SUM(AB20:AB21)</x:f>
+        <x:v>480.7692307692307</x:v>
+      </x:c>
+      <x:c r="AC31" s="37" t="n">
+        <x:f>AB31+SUM(AC20:AC21)</x:f>
+        <x:v>499.99999999999994</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="1"/>
@@ -4854,11 +6916,10 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="D4:F4"/>
-    <x:mergeCell ref="C23:L24"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="D18:P18">
-    <x:cfRule type="expression" dxfId="0" priority="1">
-      <x:formula>D18&lt;D19</x:formula>
+  <x:conditionalFormatting sqref="D27:AC27">
+    <x:cfRule type="expression" dxfId="1" priority="1">
+      <x:formula>D27&lt;D28</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6704,7 +8765,7 @@
       <x:c r="C17" s="1" t="str">
         <x:v>Net cash variance</x:v>
       </x:c>
-      <x:c r="D17" s="6" t="n">
+      <x:c r="D17" s="29" t="n">
         <x:f>SUM(J7:J10)</x:f>
         <x:v>-12000</x:v>
       </x:c>
@@ -7404,6 +9465,1351 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="2" t="str">
+        <x:v>Synthetic invoices issued during forecast</x:v>
+      </x:c>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+      <x:c r="L3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1" t="str">
+        <x:v>Case selected</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:f>'Assumptions'!D4</x:f>
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+      <x:c r="K4" s="1"/>
+      <x:c r="L4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="1"/>
+      <x:c r="B5" s="1"/>
+      <x:c r="C5" s="1"/>
+      <x:c r="D5" s="1"/>
+      <x:c r="E5" s="1"/>
+      <x:c r="F5" s="1"/>
+      <x:c r="G5" s="1"/>
+      <x:c r="H5" s="1"/>
+      <x:c r="I5" s="1"/>
+      <x:c r="J5" s="1"/>
+      <x:c r="K5" s="1"/>
+      <x:c r="L5" s="1"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="1"/>
+      <x:c r="B6" s="1"/>
+      <x:c r="C6" s="14" t="str">
+        <x:v>Invoice ID</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>Issue week</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>Amount USD</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>Collection week</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>Collection date</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>Opening AR?</x:v>
+      </x:c>
+      <x:c r="I6" s="1"/>
+      <x:c r="J6" s="1"/>
+      <x:c r="K6" s="1"/>
+      <x:c r="L6" s="1"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="1"/>
+      <x:c r="B7" s="1"/>
+      <x:c r="C7" s="5" t="str">
+        <x:v>NEW-2001</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="n">
+        <x:f>D7+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G7" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F7-1)</x:f>
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I7" s="1"/>
+      <x:c r="J7" s="1"/>
+      <x:c r="K7" s="1"/>
+      <x:c r="L7" s="1"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="1"/>
+      <x:c r="B8" s="1"/>
+      <x:c r="C8" s="5" t="str">
+        <x:v>NEW-2002</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F8" s="16" t="n">
+        <x:f>D8+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F8-1)</x:f>
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I8" s="1"/>
+      <x:c r="J8" s="1"/>
+      <x:c r="K8" s="1"/>
+      <x:c r="L8" s="1"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="1"/>
+      <x:c r="C9" s="5" t="str">
+        <x:v>NEW-2003</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="n">
+        <x:f>D9+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F9-1)</x:f>
+        <x:v>46328</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I9" s="1"/>
+      <x:c r="J9" s="1"/>
+      <x:c r="K9" s="1"/>
+      <x:c r="L9" s="1"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="1"/>
+      <x:c r="C10" s="5" t="str">
+        <x:v>NEW-2004</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="n">
+        <x:f>D10+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G10" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F10-1)</x:f>
+        <x:v>46335</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I10" s="1"/>
+      <x:c r="J10" s="1"/>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="1"/>
+      <x:c r="B11" s="1"/>
+      <x:c r="C11" s="5" t="str">
+        <x:v>NEW-2005</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="n">
+        <x:f>D11+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G11" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F11-1)</x:f>
+        <x:v>46342</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I11" s="1"/>
+      <x:c r="J11" s="1"/>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="1"/>
+      <x:c r="B12" s="1"/>
+      <x:c r="C12" s="5" t="str">
+        <x:v>NEW-2006</x:v>
+      </x:c>
+      <x:c r="D12" s="5" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="n">
+        <x:f>D12+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G12" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F12-1)</x:f>
+        <x:v>46349</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I12" s="1"/>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="1"/>
+      <x:c r="B13" s="1"/>
+      <x:c r="C13" s="5" t="str">
+        <x:v>NEW-2007</x:v>
+      </x:c>
+      <x:c r="D13" s="5" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="n">
+        <x:f>D13+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G13" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F13-1)</x:f>
+        <x:v>46356</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I13" s="1"/>
+      <x:c r="J13" s="1"/>
+      <x:c r="K13" s="1"/>
+      <x:c r="L13" s="1"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="1"/>
+      <x:c r="B14" s="1"/>
+      <x:c r="C14" s="5" t="str">
+        <x:v>NEW-2008</x:v>
+      </x:c>
+      <x:c r="D14" s="5" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="n">
+        <x:f>D14+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G14" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F14-1)</x:f>
+        <x:v>46363</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I14" s="1"/>
+      <x:c r="J14" s="1"/>
+      <x:c r="K14" s="1"/>
+      <x:c r="L14" s="1"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="1"/>
+      <x:c r="B15" s="1"/>
+      <x:c r="C15" s="5" t="str">
+        <x:v>NEW-2009</x:v>
+      </x:c>
+      <x:c r="D15" s="5" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="n">
+        <x:f>D15+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G15" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F15-1)</x:f>
+        <x:v>46370</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I15" s="1"/>
+      <x:c r="J15" s="1"/>
+      <x:c r="K15" s="1"/>
+      <x:c r="L15" s="1"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="1"/>
+      <x:c r="C16" s="5" t="str">
+        <x:v>NEW-2010</x:v>
+      </x:c>
+      <x:c r="D16" s="5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="n">
+        <x:f>D16+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G16" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F16-1)</x:f>
+        <x:v>46377</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I16" s="1"/>
+      <x:c r="J16" s="1"/>
+      <x:c r="K16" s="1"/>
+      <x:c r="L16" s="1"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="5" t="str">
+        <x:v>NEW-2011</x:v>
+      </x:c>
+      <x:c r="D17" s="5" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="n">
+        <x:f>D17+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G17" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F17-1)</x:f>
+        <x:v>46384</x:v>
+      </x:c>
+      <x:c r="H17" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I17" s="1"/>
+      <x:c r="J17" s="1"/>
+      <x:c r="K17" s="1"/>
+      <x:c r="L17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="5" t="str">
+        <x:v>NEW-2012</x:v>
+      </x:c>
+      <x:c r="D18" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="n">
+        <x:f>D18+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G18" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F18-1)</x:f>
+        <x:v>46391</x:v>
+      </x:c>
+      <x:c r="H18" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I18" s="1"/>
+      <x:c r="J18" s="1"/>
+      <x:c r="K18" s="1"/>
+      <x:c r="L18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="5" t="str">
+        <x:v>NEW-2013</x:v>
+      </x:c>
+      <x:c r="D19" s="5" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="n">
+        <x:f>D19+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G19" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F19-1)</x:f>
+        <x:v>46398</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I19" s="1"/>
+      <x:c r="J19" s="1"/>
+      <x:c r="K19" s="1"/>
+      <x:c r="L19" s="1"/>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="5" t="str">
+        <x:v>NEW-2014</x:v>
+      </x:c>
+      <x:c r="D20" s="5" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="n">
+        <x:f>D20+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G20" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F20-1)</x:f>
+        <x:v>46405</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I20" s="1"/>
+      <x:c r="J20" s="1"/>
+      <x:c r="K20" s="1"/>
+      <x:c r="L20" s="1"/>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="1"/>
+      <x:c r="B21" s="1"/>
+      <x:c r="C21" s="5" t="str">
+        <x:v>NEW-2015</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="n">
+        <x:f>D21+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G21" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F21-1)</x:f>
+        <x:v>46412</x:v>
+      </x:c>
+      <x:c r="H21" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I21" s="1"/>
+      <x:c r="J21" s="1"/>
+      <x:c r="K21" s="1"/>
+      <x:c r="L21" s="1"/>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="5" t="str">
+        <x:v>NEW-2016</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="n">
+        <x:f>D22+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G22" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F22-1)</x:f>
+        <x:v>46419</x:v>
+      </x:c>
+      <x:c r="H22" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I22" s="1"/>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="1"/>
+      <x:c r="L22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="1"/>
+      <x:c r="B23" s="1"/>
+      <x:c r="C23" s="5" t="str">
+        <x:v>NEW-2017</x:v>
+      </x:c>
+      <x:c r="D23" s="5" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="n">
+        <x:f>D23+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G23" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F23-1)</x:f>
+        <x:v>46426</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I23" s="1"/>
+      <x:c r="J23" s="1"/>
+      <x:c r="K23" s="1"/>
+      <x:c r="L23" s="1"/>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="5" t="str">
+        <x:v>NEW-2018</x:v>
+      </x:c>
+      <x:c r="D24" s="5" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="n">
+        <x:f>D24+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G24" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F24-1)</x:f>
+        <x:v>46433</x:v>
+      </x:c>
+      <x:c r="H24" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I24" s="1"/>
+      <x:c r="J24" s="1"/>
+      <x:c r="K24" s="1"/>
+      <x:c r="L24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="5" t="str">
+        <x:v>NEW-2019</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E25" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="n">
+        <x:f>D25+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G25" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F25-1)</x:f>
+        <x:v>46440</x:v>
+      </x:c>
+      <x:c r="H25" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I25" s="1"/>
+      <x:c r="J25" s="1"/>
+      <x:c r="K25" s="1"/>
+      <x:c r="L25" s="1"/>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="5" t="str">
+        <x:v>NEW-2020</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E26" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F26" s="16" t="n">
+        <x:f>D26+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G26" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F26-1)</x:f>
+        <x:v>46447</x:v>
+      </x:c>
+      <x:c r="H26" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I26" s="1"/>
+      <x:c r="J26" s="1"/>
+      <x:c r="K26" s="1"/>
+      <x:c r="L26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="1"/>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="5" t="str">
+        <x:v>NEW-2021</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E27" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="n">
+        <x:f>D27+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G27" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F27-1)</x:f>
+        <x:v>46454</x:v>
+      </x:c>
+      <x:c r="H27" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I27" s="1"/>
+      <x:c r="J27" s="1"/>
+      <x:c r="K27" s="1"/>
+      <x:c r="L27" s="1"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="5" t="str">
+        <x:v>NEW-2022</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E28" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="n">
+        <x:f>D28+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G28" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F28-1)</x:f>
+        <x:v>46461</x:v>
+      </x:c>
+      <x:c r="H28" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I28" s="1"/>
+      <x:c r="J28" s="1"/>
+      <x:c r="K28" s="1"/>
+      <x:c r="L28" s="1"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="5" t="str">
+        <x:v>NEW-2023</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E29" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="n">
+        <x:f>D29+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G29" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F29-1)</x:f>
+        <x:v>46468</x:v>
+      </x:c>
+      <x:c r="H29" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I29" s="1"/>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="1"/>
+      <x:c r="L29" s="1"/>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="5" t="str">
+        <x:v>NEW-2024</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E30" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F30" s="16" t="n">
+        <x:f>D30+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G30" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F30-1)</x:f>
+        <x:v>46475</x:v>
+      </x:c>
+      <x:c r="H30" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I30" s="1"/>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="5" t="str">
+        <x:v>NEW-2025</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E31" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F31" s="16" t="n">
+        <x:f>D31+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G31" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F31-1)</x:f>
+        <x:v>46482</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I31" s="1"/>
+      <x:c r="J31" s="1"/>
+      <x:c r="K31" s="1"/>
+      <x:c r="L31" s="1"/>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="1"/>
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="5" t="str">
+        <x:v>NEW-2026</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E32" s="30" t="n">
+        <x:f>'Assumptions'!$I$39</x:f>
+        <x:v>92000</x:v>
+      </x:c>
+      <x:c r="F32" s="16" t="n">
+        <x:f>D32+'Assumptions'!$I$40+'Assumptions'!$D$8</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G32" s="19" t="n">
+        <x:f>DATE(2026,10,5)+7*(F32-1)</x:f>
+        <x:v>46489</x:v>
+      </x:c>
+      <x:c r="H32" s="5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I32" s="1"/>
+      <x:c r="J32" s="1"/>
+      <x:c r="K32" s="1"/>
+      <x:c r="L32" s="1"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1"/>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="1"/>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1"/>
+      <x:c r="H33" s="1"/>
+      <x:c r="I33" s="1"/>
+      <x:c r="J33" s="1"/>
+      <x:c r="K33" s="1"/>
+      <x:c r="L33" s="1"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+      <x:c r="I34" s="1"/>
+      <x:c r="J34" s="1"/>
+      <x:c r="K34" s="1"/>
+      <x:c r="L34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="1"/>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1"/>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="1"/>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1"/>
+      <x:c r="H35" s="1"/>
+      <x:c r="I35" s="1"/>
+      <x:c r="J35" s="1"/>
+      <x:c r="K35" s="1"/>
+      <x:c r="L35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
+      <x:c r="I36" s="1"/>
+      <x:c r="J36" s="1"/>
+      <x:c r="K36" s="1"/>
+      <x:c r="L36" s="1"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="1"/>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="1"/>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1"/>
+      <x:c r="H37" s="1"/>
+      <x:c r="I37" s="1"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="1"/>
+      <x:c r="D38" s="1"/>
+      <x:c r="E38" s="1"/>
+      <x:c r="F38" s="1"/>
+      <x:c r="G38" s="1"/>
+      <x:c r="H38" s="1"/>
+      <x:c r="I38" s="1"/>
+      <x:c r="J38" s="1"/>
+      <x:c r="K38" s="1"/>
+      <x:c r="L38" s="1"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="1"/>
+      <x:c r="B39" s="1"/>
+      <x:c r="C39" s="1"/>
+      <x:c r="D39" s="1"/>
+      <x:c r="E39" s="1"/>
+      <x:c r="F39" s="1"/>
+      <x:c r="G39" s="1"/>
+      <x:c r="H39" s="1"/>
+      <x:c r="I39" s="1"/>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="1"/>
+      <x:c r="B40" s="1"/>
+      <x:c r="C40" s="1"/>
+      <x:c r="D40" s="1"/>
+      <x:c r="E40" s="1"/>
+      <x:c r="F40" s="1"/>
+      <x:c r="G40" s="1"/>
+      <x:c r="H40" s="1"/>
+      <x:c r="I40" s="1"/>
+      <x:c r="J40" s="1"/>
+      <x:c r="K40" s="1"/>
+      <x:c r="L40" s="1"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="1"/>
+      <x:c r="C41" s="1"/>
+      <x:c r="D41" s="1"/>
+      <x:c r="E41" s="1"/>
+      <x:c r="F41" s="1"/>
+      <x:c r="G41" s="1"/>
+      <x:c r="H41" s="1"/>
+      <x:c r="I41" s="1"/>
+      <x:c r="J41" s="1"/>
+      <x:c r="K41" s="1"/>
+      <x:c r="L41" s="1"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="1"/>
+      <x:c r="B42" s="1"/>
+      <x:c r="C42" s="1"/>
+      <x:c r="D42" s="1"/>
+      <x:c r="E42" s="1"/>
+      <x:c r="F42" s="1"/>
+      <x:c r="G42" s="1"/>
+      <x:c r="H42" s="1"/>
+      <x:c r="I42" s="1"/>
+      <x:c r="J42" s="1"/>
+      <x:c r="K42" s="1"/>
+      <x:c r="L42" s="1"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="1"/>
+      <x:c r="B43" s="1"/>
+      <x:c r="C43" s="1"/>
+      <x:c r="D43" s="1"/>
+      <x:c r="E43" s="1"/>
+      <x:c r="F43" s="1"/>
+      <x:c r="G43" s="1"/>
+      <x:c r="H43" s="1"/>
+      <x:c r="I43" s="1"/>
+      <x:c r="J43" s="1"/>
+      <x:c r="K43" s="1"/>
+      <x:c r="L43" s="1"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="1"/>
+      <x:c r="C44" s="1"/>
+      <x:c r="D44" s="1"/>
+      <x:c r="E44" s="1"/>
+      <x:c r="F44" s="1"/>
+      <x:c r="G44" s="1"/>
+      <x:c r="H44" s="1"/>
+      <x:c r="I44" s="1"/>
+      <x:c r="J44" s="1"/>
+      <x:c r="K44" s="1"/>
+      <x:c r="L44" s="1"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="1"/>
+      <x:c r="B45" s="1"/>
+      <x:c r="C45" s="1"/>
+      <x:c r="D45" s="1"/>
+      <x:c r="E45" s="1"/>
+      <x:c r="F45" s="1"/>
+      <x:c r="G45" s="1"/>
+      <x:c r="H45" s="1"/>
+      <x:c r="I45" s="1"/>
+      <x:c r="J45" s="1"/>
+      <x:c r="K45" s="1"/>
+      <x:c r="L45" s="1"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="1"/>
+      <x:c r="B46" s="1"/>
+      <x:c r="C46" s="1"/>
+      <x:c r="D46" s="1"/>
+      <x:c r="E46" s="1"/>
+      <x:c r="F46" s="1"/>
+      <x:c r="G46" s="1"/>
+      <x:c r="H46" s="1"/>
+      <x:c r="I46" s="1"/>
+      <x:c r="J46" s="1"/>
+      <x:c r="K46" s="1"/>
+      <x:c r="L46" s="1"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="1"/>
+      <x:c r="C47" s="1"/>
+      <x:c r="D47" s="1"/>
+      <x:c r="E47" s="1"/>
+      <x:c r="F47" s="1"/>
+      <x:c r="G47" s="1"/>
+      <x:c r="H47" s="1"/>
+      <x:c r="I47" s="1"/>
+      <x:c r="J47" s="1"/>
+      <x:c r="K47" s="1"/>
+      <x:c r="L47" s="1"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="1"/>
+      <x:c r="B48" s="1"/>
+      <x:c r="C48" s="1"/>
+      <x:c r="D48" s="1"/>
+      <x:c r="E48" s="1"/>
+      <x:c r="F48" s="1"/>
+      <x:c r="G48" s="1"/>
+      <x:c r="H48" s="1"/>
+      <x:c r="I48" s="1"/>
+      <x:c r="J48" s="1"/>
+      <x:c r="K48" s="1"/>
+      <x:c r="L48" s="1"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1"/>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1"/>
+      <x:c r="F49" s="1"/>
+      <x:c r="G49" s="1"/>
+      <x:c r="H49" s="1"/>
+      <x:c r="I49" s="1"/>
+      <x:c r="J49" s="1"/>
+      <x:c r="K49" s="1"/>
+      <x:c r="L49" s="1"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="1"/>
+      <x:c r="B50" s="1"/>
+      <x:c r="C50" s="1"/>
+      <x:c r="D50" s="1"/>
+      <x:c r="E50" s="1"/>
+      <x:c r="F50" s="1"/>
+      <x:c r="G50" s="1"/>
+      <x:c r="H50" s="1"/>
+      <x:c r="I50" s="1"/>
+      <x:c r="J50" s="1"/>
+      <x:c r="K50" s="1"/>
+      <x:c r="L50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="1"/>
+      <x:c r="B51" s="1"/>
+      <x:c r="C51" s="1"/>
+      <x:c r="D51" s="1"/>
+      <x:c r="E51" s="1"/>
+      <x:c r="F51" s="1"/>
+      <x:c r="G51" s="1"/>
+      <x:c r="H51" s="1"/>
+      <x:c r="I51" s="1"/>
+      <x:c r="J51" s="1"/>
+      <x:c r="K51" s="1"/>
+      <x:c r="L51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="1"/>
+      <x:c r="B52" s="1"/>
+      <x:c r="C52" s="1"/>
+      <x:c r="D52" s="1"/>
+      <x:c r="E52" s="1"/>
+      <x:c r="F52" s="1"/>
+      <x:c r="G52" s="1"/>
+      <x:c r="H52" s="1"/>
+      <x:c r="I52" s="1"/>
+      <x:c r="J52" s="1"/>
+      <x:c r="K52" s="1"/>
+      <x:c r="L52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="1"/>
+      <x:c r="B53" s="1"/>
+      <x:c r="C53" s="1"/>
+      <x:c r="D53" s="1"/>
+      <x:c r="E53" s="1"/>
+      <x:c r="F53" s="1"/>
+      <x:c r="G53" s="1"/>
+      <x:c r="H53" s="1"/>
+      <x:c r="I53" s="1"/>
+      <x:c r="J53" s="1"/>
+      <x:c r="K53" s="1"/>
+      <x:c r="L53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="1"/>
+      <x:c r="B54" s="1"/>
+      <x:c r="C54" s="1"/>
+      <x:c r="D54" s="1"/>
+      <x:c r="E54" s="1"/>
+      <x:c r="F54" s="1"/>
+      <x:c r="G54" s="1"/>
+      <x:c r="H54" s="1"/>
+      <x:c r="I54" s="1"/>
+      <x:c r="J54" s="1"/>
+      <x:c r="K54" s="1"/>
+      <x:c r="L54" s="1"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1"/>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1"/>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="1"/>
+      <x:c r="H55" s="1"/>
+      <x:c r="I55" s="1"/>
+      <x:c r="J55" s="1"/>
+      <x:c r="K55" s="1"/>
+      <x:c r="L55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="1"/>
+      <x:c r="B56" s="1"/>
+      <x:c r="C56" s="1"/>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1"/>
+      <x:c r="F56" s="1"/>
+      <x:c r="G56" s="1"/>
+      <x:c r="H56" s="1"/>
+      <x:c r="I56" s="1"/>
+      <x:c r="J56" s="1"/>
+      <x:c r="K56" s="1"/>
+      <x:c r="L56" s="1"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
+      <x:c r="I57" s="1"/>
+      <x:c r="J57" s="1"/>
+      <x:c r="K57" s="1"/>
+      <x:c r="L57" s="1"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="1"/>
+      <x:c r="B58" s="1"/>
+      <x:c r="C58" s="1"/>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1"/>
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="1"/>
+      <x:c r="H58" s="1"/>
+      <x:c r="I58" s="1"/>
+      <x:c r="J58" s="1"/>
+      <x:c r="K58" s="1"/>
+      <x:c r="L58" s="1"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="1"/>
+      <x:c r="B59" s="1"/>
+      <x:c r="C59" s="1"/>
+      <x:c r="D59" s="1"/>
+      <x:c r="E59" s="1"/>
+      <x:c r="F59" s="1"/>
+      <x:c r="G59" s="1"/>
+      <x:c r="H59" s="1"/>
+      <x:c r="I59" s="1"/>
+      <x:c r="J59" s="1"/>
+      <x:c r="K59" s="1"/>
+      <x:c r="L59" s="1"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="1"/>
+      <x:c r="B60" s="1"/>
+      <x:c r="C60" s="1"/>
+      <x:c r="D60" s="1"/>
+      <x:c r="E60" s="1"/>
+      <x:c r="F60" s="1"/>
+      <x:c r="G60" s="1"/>
+      <x:c r="H60" s="1"/>
+      <x:c r="I60" s="1"/>
+      <x:c r="J60" s="1"/>
+      <x:c r="K60" s="1"/>
+      <x:c r="L60" s="1"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+      <x:c r="I61" s="1"/>
+      <x:c r="J61" s="1"/>
+      <x:c r="K61" s="1"/>
+      <x:c r="L61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="1"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62" s="1"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62" s="1"/>
+      <x:c r="H62" s="1"/>
+      <x:c r="I62" s="1"/>
+      <x:c r="J62" s="1"/>
+      <x:c r="K62" s="1"/>
+      <x:c r="L62" s="1"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
+      <x:c r="I63" s="1"/>
+      <x:c r="J63" s="1"/>
+      <x:c r="K63" s="1"/>
+      <x:c r="L63" s="1"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="1"/>
+      <x:c r="B64" s="1"/>
+      <x:c r="C64" s="1"/>
+      <x:c r="D64" s="1"/>
+      <x:c r="E64" s="1"/>
+      <x:c r="F64" s="1"/>
+      <x:c r="G64" s="1"/>
+      <x:c r="H64" s="1"/>
+      <x:c r="I64" s="1"/>
+      <x:c r="J64" s="1"/>
+      <x:c r="K64" s="1"/>
+      <x:c r="L64" s="1"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+      <x:c r="I65" s="1"/>
+      <x:c r="J65" s="1"/>
+      <x:c r="K65" s="1"/>
+      <x:c r="L65" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="D4:F4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -8422,7 +11828,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -8538,11 +11944,11 @@
       <x:c r="C7" s="5" t="str">
         <x:v>Invoices collected plus carried forward</x:v>
       </x:c>
-      <x:c r="D7" s="34" t="n">
-        <x:f>SUM('Invoices'!F7:F32)-SUM('Weekly'!D8:P8)-'Summary'!D10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="35" t="n">
+      <x:c r="D7" s="40" t="n">
+        <x:f>SUM('Invoices'!F7:F32,'New Invoices'!E7:E32)-SUM('Weekly'!D8:AC8,'Weekly'!D10:AC10)-'Summary'!D10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="40" t="n">
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F7" s="1"/>
@@ -8559,11 +11965,11 @@
       <x:c r="C8" s="5" t="str">
         <x:v>Cash roll-forward</x:v>
       </x:c>
-      <x:c r="D8" s="34" t="n">
-        <x:f>'Weekly'!P18-'Assumptions'!G9-SUM('Weekly'!D17:P17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="n">
+      <x:c r="D8" s="40" t="n">
+        <x:f>'Weekly'!AC27-'Assumptions'!G9-SUM('Weekly'!D18:AC18,'Weekly'!D24:AC24)+SUM('Weekly'!D20:AC21,'Weekly'!D25:AC25)</x:f>
+        <x:v>4.6560444388887845e-10</x:v>
+      </x:c>
+      <x:c r="E8" s="40" t="n">
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F8" s="1"/>
@@ -8580,11 +11986,11 @@
       <x:c r="C9" s="5" t="str">
         <x:v>Capex paid plus future obligation</x:v>
       </x:c>
-      <x:c r="D9" s="34" t="n">
-        <x:f>'Assumptions'!G16-SUM('Weekly'!D15:P15)-'Summary'!D11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="n">
+      <x:c r="D9" s="40" t="n">
+        <x:f>'Assumptions'!G16-SUM('Weekly'!D16:AC16)-'Summary'!D11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="40" t="n">
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F9" s="1"/>
@@ -8601,11 +12007,11 @@
       <x:c r="C10" s="5" t="str">
         <x:v>Simulated review bridge</x:v>
       </x:c>
-      <x:c r="D10" s="34" t="n">
+      <x:c r="D10" s="40" t="n">
         <x:f>SUM('Review'!J7:J10)-SUM('Review'!F7:F10)+SUM('Review'!I7:I10)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="35" t="n">
+      <x:c r="E10" s="40" t="n">
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F10" s="1"/>
@@ -9388,7 +12794,7 @@
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
-    <x:cfRule type="expression" dxfId="1" priority="1">
+    <x:cfRule type="expression" dxfId="2" priority="1">
       <x:formula>ABS(D7)&gt;E7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
